--- a/output/general/production_comparisons_latest.xlsx
+++ b/output/general/production_comparisons_latest.xlsx
@@ -436,129 +436,93 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C2" t="n">
-        <v>111</v>
-      </c>
+        <v>2006</v>
+      </c>
+      <c r="C2"/>
       <c r="D2" t="n">
-        <v>111</v>
-      </c>
-      <c r="E2" t="n">
-        <v>111</v>
-      </c>
-      <c r="F2" t="n">
-        <v>841047</v>
-      </c>
-      <c r="G2" t="n">
-        <v>842599.936</v>
-      </c>
-      <c r="H2" t="n">
-        <v>841000</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C3" t="n">
-        <v>86</v>
-      </c>
+        <v>2007</v>
+      </c>
+      <c r="C3"/>
       <c r="D3" t="n">
-        <v>86</v>
-      </c>
-      <c r="E3" t="n">
-        <v>86</v>
-      </c>
-      <c r="F3" t="n">
-        <v>538016</v>
-      </c>
-      <c r="G3" t="n">
-        <v>538193.24</v>
-      </c>
-      <c r="H3" t="n">
-        <v>538347</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>2020</v>
+        <v>2008</v>
       </c>
       <c r="C4" t="n">
-        <v>209</v>
+        <v>504</v>
       </c>
       <c r="D4" t="n">
-        <v>209</v>
-      </c>
-      <c r="E4" t="n">
-        <v>209</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E4"/>
       <c r="F4" t="n">
-        <v>1394030</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1396408.512</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1394030</v>
-      </c>
+        <v>2671068</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>2021</v>
+        <v>2009</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>2304</v>
       </c>
       <c r="D5" t="n">
-        <v>223</v>
-      </c>
-      <c r="E5" t="n">
-        <v>223</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="E5"/>
       <c r="F5" t="n">
-        <v>1447493</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1446424.525</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1447320</v>
-      </c>
+        <v>16868720</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C6" t="n">
-        <v>243</v>
-      </c>
+        <v>2010</v>
+      </c>
+      <c r="C6"/>
       <c r="D6" t="n">
-        <v>243</v>
+        <v>539</v>
       </c>
       <c r="E6" t="n">
-        <v>243</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1738908</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="F6"/>
       <c r="G6" t="n">
-        <v>1740569.1</v>
+        <v>4016295.712</v>
       </c>
       <c r="H6" t="n">
-        <v>1739960</v>
+        <v>4007000</v>
       </c>
     </row>
     <row r="7">
@@ -566,25 +530,21 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C7" t="n">
-        <v>261</v>
-      </c>
+        <v>2011</v>
+      </c>
+      <c r="C7"/>
       <c r="D7" t="n">
-        <v>261</v>
+        <v>101</v>
       </c>
       <c r="E7" t="n">
-        <v>261</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2145942</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="F7"/>
       <c r="G7" t="n">
-        <v>1830556.728</v>
+        <v>582872.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1832170</v>
+        <v>581000</v>
       </c>
     </row>
     <row r="8">
@@ -592,714 +552,2124 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C8" t="n">
-        <v>253</v>
-      </c>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8" t="n">
-        <v>3017531</v>
-      </c>
-      <c r="G8"/>
-      <c r="H8"/>
+        <v>2012</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8" t="n">
+        <v>277</v>
+      </c>
+      <c r="E8" t="n">
+        <v>277</v>
+      </c>
+      <c r="F8"/>
+      <c r="G8" t="n">
+        <v>2535975.706</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2036000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C9" t="n">
-        <v>78721</v>
-      </c>
+        <v>2013</v>
+      </c>
+      <c r="C9"/>
       <c r="D9" t="n">
-        <v>19680.308</v>
+        <v>212</v>
       </c>
       <c r="E9" t="n">
-        <v>19681</v>
-      </c>
-      <c r="F9" t="n">
-        <v>479915638.8108</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="F9"/>
       <c r="G9" t="n">
-        <v>120201505.184</v>
+        <v>1208540.19</v>
       </c>
       <c r="H9" t="n">
-        <v>119981000</v>
+        <v>1009000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C10" t="n">
-        <v>81775.78</v>
+        <v>856</v>
       </c>
       <c r="D10" t="n">
-        <v>20442.966</v>
+        <v>214</v>
       </c>
       <c r="E10" t="n">
-        <v>20443.945</v>
+        <v>214</v>
       </c>
       <c r="F10" t="n">
-        <v>482748849.556</v>
+        <v>3862717.12</v>
       </c>
       <c r="G10" t="n">
-        <v>121180584.899</v>
+        <v>1219265.872</v>
       </c>
       <c r="H10" t="n">
-        <v>120687212</v>
+        <v>1018000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C11" t="n">
-        <v>87082.76</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>21718.27</v>
+        <v>82</v>
       </c>
       <c r="E11" t="n">
-        <v>21771.42</v>
+        <v>82</v>
       </c>
       <c r="F11" t="n">
-        <v>531771831.1712</v>
+        <v>665984</v>
       </c>
       <c r="G11" t="n">
-        <v>132723081.339</v>
+        <v>540421.574</v>
       </c>
       <c r="H11" t="n">
-        <v>132947876</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C12" t="n">
-        <v>123190.456</v>
+        <v>44</v>
       </c>
       <c r="D12" t="n">
-        <v>27919.701</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
-        <v>26830.7</v>
+        <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>694026961.3224</v>
+        <v>452012</v>
       </c>
       <c r="G12" t="n">
-        <v>167033674.015</v>
+        <v>440281.448</v>
       </c>
       <c r="H12" t="n">
-        <v>162243534</v>
+        <v>452000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C13" t="n">
-        <v>120126.94</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>27217.793</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
-        <v>27197.37</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>740738277.8382</v>
+        <v>570525</v>
       </c>
       <c r="G13" t="n">
-        <v>177813277.45</v>
+        <v>686889.252</v>
       </c>
       <c r="H13" t="n">
-        <v>177097530</v>
+        <v>683000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="C14" t="n">
-        <v>84254.3057</v>
+        <v>111</v>
       </c>
       <c r="D14" t="n">
-        <v>26823.903</v>
+        <v>111</v>
       </c>
       <c r="E14" t="n">
-        <v>26859.11</v>
+        <v>111</v>
       </c>
       <c r="F14" t="n">
-        <v>625028159.5993</v>
+        <v>841047</v>
       </c>
       <c r="G14" t="n">
-        <v>203583873.108</v>
+        <v>842599.936</v>
       </c>
       <c r="H14" t="n">
-        <v>203839780</v>
+        <v>841000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="C15" t="n">
-        <v>90884.2487</v>
-      </c>
-      <c r="D15"/>
-      <c r="E15"/>
+        <v>86</v>
+      </c>
+      <c r="D15" t="n">
+        <v>86</v>
+      </c>
+      <c r="E15" t="n">
+        <v>86</v>
+      </c>
       <c r="F15" t="n">
-        <v>595783690.3707</v>
-      </c>
-      <c r="G15"/>
-      <c r="H15"/>
+        <v>538016</v>
+      </c>
+      <c r="G15" t="n">
+        <v>538193.24</v>
+      </c>
+      <c r="H15" t="n">
+        <v>538347</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C16" t="n">
-        <v>71601.596</v>
+        <v>209</v>
       </c>
       <c r="D16" t="n">
-        <v>17852.3</v>
+        <v>209</v>
       </c>
       <c r="E16" t="n">
-        <v>17899</v>
+        <v>209</v>
       </c>
       <c r="F16" t="n">
-        <v>155019979.1364</v>
+        <v>1394030</v>
       </c>
       <c r="G16" t="n">
-        <v>38447654.32</v>
+        <v>1396408.512</v>
       </c>
       <c r="H16" t="n">
-        <v>38756000</v>
+        <v>1394030</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B17" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C17" t="n">
-        <v>69260.48</v>
+        <v>223</v>
       </c>
       <c r="D17" t="n">
-        <v>17283.305</v>
+        <v>223</v>
       </c>
       <c r="E17" t="n">
-        <v>17315.12</v>
+        <v>223</v>
       </c>
       <c r="F17" t="n">
-        <v>143941353.3624</v>
+        <v>1447493</v>
       </c>
       <c r="G17" t="n">
-        <v>36041258.536</v>
+        <v>1446424.525</v>
       </c>
       <c r="H17" t="n">
-        <v>35985337</v>
+        <v>1447320</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B18" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C18" t="n">
-        <v>73540.472</v>
+        <v>243</v>
       </c>
       <c r="D18" t="n">
-        <v>18435.87</v>
+        <v>243</v>
       </c>
       <c r="E18" t="n">
-        <v>22209.728</v>
+        <v>243</v>
       </c>
       <c r="F18" t="n">
-        <v>139367549.7104</v>
+        <v>1738908</v>
       </c>
       <c r="G18" t="n">
-        <v>35610954.217</v>
+        <v>1740569.1</v>
       </c>
       <c r="H18" t="n">
-        <v>41354066</v>
+        <v>1739960</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B19" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C19" t="n">
-        <v>71822.516</v>
+        <v>261</v>
       </c>
       <c r="D19" t="n">
-        <v>18024.757</v>
+        <v>261</v>
       </c>
       <c r="E19" t="n">
-        <v>17955.629</v>
+        <v>261</v>
       </c>
       <c r="F19" t="n">
-        <v>155082427.8898</v>
+        <v>2145942</v>
       </c>
       <c r="G19" t="n">
-        <v>38483581.5</v>
+        <v>1830556.728</v>
       </c>
       <c r="H19" t="n">
-        <v>38770609</v>
+        <v>1832170</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B20" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C20" t="n">
-        <v>74827.296</v>
-      </c>
-      <c r="D20" t="n">
-        <v>18557.112</v>
-      </c>
-      <c r="E20" t="n">
-        <v>18706.84</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="D20"/>
+      <c r="E20"/>
       <c r="F20" t="n">
-        <v>213208582.5488</v>
-      </c>
-      <c r="G20" t="n">
-        <v>54304484.25</v>
-      </c>
-      <c r="H20" t="n">
-        <v>53302146</v>
-      </c>
+        <v>3017531</v>
+      </c>
+      <c r="G20"/>
+      <c r="H20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C21" t="n">
-        <v>71394.22</v>
-      </c>
+        <v>2006</v>
+      </c>
+      <c r="C21"/>
       <c r="D21" t="n">
-        <v>17785.024</v>
-      </c>
-      <c r="E21" t="n">
-        <v>17848.56</v>
-      </c>
-      <c r="F21" t="n">
-        <v>237492371.82</v>
-      </c>
-      <c r="G21" t="n">
-        <v>61300859.004</v>
-      </c>
-      <c r="H21" t="n">
-        <v>59373100</v>
-      </c>
+        <v>18847</v>
+      </c>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C22" t="n">
-        <v>77942.236</v>
-      </c>
-      <c r="D22"/>
+        <v>2007</v>
+      </c>
+      <c r="C22"/>
+      <c r="D22" t="n">
+        <v>16135</v>
+      </c>
       <c r="E22"/>
-      <c r="F22" t="n">
-        <v>238497122.827</v>
-      </c>
+      <c r="F22"/>
       <c r="G22"/>
       <c r="H22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B23" t="n">
-        <v>2018</v>
+        <v>2008</v>
       </c>
       <c r="C23" t="n">
-        <v>212016.4</v>
+        <v>65546</v>
       </c>
       <c r="D23" t="n">
-        <v>53542</v>
-      </c>
-      <c r="E23" t="n">
-        <v>53004</v>
-      </c>
-      <c r="F23" t="n">
-        <v>382203365.6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>99719527.984</v>
-      </c>
-      <c r="H23" t="n">
-        <v>95551000</v>
-      </c>
+        <v>15729</v>
+      </c>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B24" t="n">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="C24" t="n">
-        <v>125441.19</v>
+        <v>87839.3</v>
       </c>
       <c r="D24" t="n">
-        <v>45987</v>
-      </c>
-      <c r="E24" t="n">
-        <v>46340</v>
-      </c>
+        <v>16328.55</v>
+      </c>
+      <c r="E24"/>
       <c r="F24" t="n">
-        <v>185043130.59</v>
-      </c>
-      <c r="G24" t="n">
-        <v>95869742.062</v>
-      </c>
-      <c r="H24" t="n">
-        <v>84052015</v>
-      </c>
+        <v>524211688.98</v>
+      </c>
+      <c r="G24"/>
+      <c r="H24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B25" t="n">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C25" t="n">
-        <v>108142.96</v>
+        <v>84000</v>
       </c>
       <c r="D25" t="n">
-        <v>40052</v>
-      </c>
-      <c r="E25" t="n">
-        <v>40167.6</v>
-      </c>
+        <v>15678.51</v>
+      </c>
+      <c r="E25"/>
       <c r="F25" t="n">
-        <v>187781438.5924</v>
+        <v>414505495.35</v>
       </c>
       <c r="G25" t="n">
-        <v>92516963.719</v>
-      </c>
-      <c r="H25" t="n">
-        <v>85509274</v>
-      </c>
+        <v>87246281.936</v>
+      </c>
+      <c r="H25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C26" t="n">
-        <v>109753.75</v>
+        <v>90568</v>
       </c>
       <c r="D26" t="n">
-        <v>40742</v>
-      </c>
-      <c r="E26" t="n">
-        <v>40526.915</v>
-      </c>
+        <v>14604</v>
+      </c>
+      <c r="E26"/>
       <c r="F26" t="n">
-        <v>246230686.5765</v>
+        <v>539441119.35</v>
       </c>
       <c r="G26" t="n">
-        <v>105762551.635</v>
-      </c>
-      <c r="H26" t="n">
-        <v>106793430</v>
-      </c>
+        <v>89904447.072</v>
+      </c>
+      <c r="H26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B27" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C27" t="n">
-        <v>101701.37</v>
+        <v>75101</v>
       </c>
       <c r="D27" t="n">
-        <v>38477</v>
-      </c>
-      <c r="E27" t="n">
-        <v>37893.79</v>
-      </c>
+        <v>11222.101</v>
+      </c>
+      <c r="E27"/>
       <c r="F27" t="n">
-        <v>227145371.17</v>
+        <v>390403073.74</v>
       </c>
       <c r="G27" t="n">
-        <v>109912830.2</v>
-      </c>
-      <c r="H27" t="n">
-        <v>110689319</v>
-      </c>
+        <v>74099806.022</v>
+      </c>
+      <c r="H27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B28" t="n">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="C28" t="n">
-        <v>109417.1</v>
+        <v>54878.82</v>
       </c>
       <c r="D28" t="n">
-        <v>41670.7</v>
+        <v>13720.21</v>
       </c>
       <c r="E28" t="n">
-        <v>41220.7</v>
+        <v>13720</v>
       </c>
       <c r="F28" t="n">
-        <v>236842499.096</v>
+        <v>315782022.17</v>
       </c>
       <c r="G28" t="n">
-        <v>119195116.656</v>
+        <v>94609507.278</v>
       </c>
       <c r="H28" t="n">
-        <v>116711880</v>
+        <v>78946000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B29" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="C29" t="n">
-        <v>83823.6</v>
-      </c>
-      <c r="D29"/>
-      <c r="E29"/>
+        <v>55071.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>13767.995</v>
+      </c>
+      <c r="E29" t="n">
+        <v>13769</v>
+      </c>
       <c r="F29" t="n">
-        <v>194350336.8082</v>
-      </c>
-      <c r="G29"/>
-      <c r="H29"/>
+        <v>309668356.9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>92745163.478</v>
+      </c>
+      <c r="H29" t="n">
+        <v>77735000</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B30" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C30" t="n">
-        <v>49193.8</v>
+        <v>67500.4</v>
       </c>
       <c r="D30" t="n">
-        <v>12298.45</v>
+        <v>16874.856</v>
       </c>
       <c r="E30" t="n">
-        <v>12300</v>
+        <v>16875</v>
       </c>
       <c r="F30" t="n">
-        <v>134230777.8394</v>
+        <v>410648746.89</v>
       </c>
       <c r="G30" t="n">
-        <v>30648544.048</v>
+        <v>102802830.592</v>
       </c>
       <c r="H30" t="n">
-        <v>33559000</v>
+        <v>102664000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B31" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C31" t="n">
-        <v>50512</v>
+        <v>69075.92</v>
       </c>
       <c r="D31" t="n">
-        <v>12847.787</v>
+        <v>17269.035</v>
       </c>
       <c r="E31" t="n">
-        <v>12628</v>
+        <v>17268</v>
       </c>
       <c r="F31" t="n">
-        <v>149937833.1108</v>
+        <v>435201313.86</v>
       </c>
       <c r="G31" t="n">
-        <v>31861870.298</v>
+        <v>108633505.528</v>
       </c>
       <c r="H31" t="n">
-        <v>37484459</v>
+        <v>108802000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B32" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C32" t="n">
-        <v>48600</v>
+        <v>68457.2</v>
       </c>
       <c r="D32" t="n">
-        <v>12371</v>
+        <v>17114.409</v>
       </c>
       <c r="E32" t="n">
-        <v>12078</v>
+        <v>17115</v>
       </c>
       <c r="F32" t="n">
-        <v>155951470.8884</v>
+        <v>403896639.441</v>
       </c>
       <c r="G32" t="n">
-        <v>39335531.998</v>
+        <v>100921951.712</v>
       </c>
       <c r="H32" t="n">
-        <v>38789821</v>
+        <v>100974000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B33" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C33" t="n">
-        <v>46856</v>
+        <v>78721</v>
       </c>
       <c r="D33" t="n">
-        <v>11714</v>
+        <v>19680.308</v>
       </c>
       <c r="E33" t="n">
-        <v>11714</v>
+        <v>19681</v>
       </c>
       <c r="F33" t="n">
-        <v>143440009.0512</v>
+        <v>479915638.8108</v>
       </c>
       <c r="G33" t="n">
-        <v>36587678.66</v>
+        <v>120201505.184</v>
       </c>
       <c r="H33" t="n">
-        <v>35860002</v>
+        <v>119981000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B34" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C34" t="n">
-        <v>44848</v>
+        <v>81775.78</v>
       </c>
       <c r="D34" t="n">
-        <v>11210.78</v>
+        <v>20442.966</v>
       </c>
       <c r="E34" t="n">
-        <v>11212</v>
+        <v>20443.945</v>
       </c>
       <c r="F34" t="n">
-        <v>164806846.6648</v>
+        <v>482748849.556</v>
       </c>
       <c r="G34" t="n">
-        <v>36065958.65</v>
+        <v>121180584.899</v>
       </c>
       <c r="H34" t="n">
-        <v>41201711</v>
+        <v>120687212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B35" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C35" t="n">
-        <v>45048</v>
+        <v>87082.76</v>
       </c>
       <c r="D35" t="n">
-        <v>11264.3</v>
+        <v>21718.27</v>
       </c>
       <c r="E35" t="n">
-        <v>11262</v>
+        <v>21771.42</v>
       </c>
       <c r="F35" t="n">
-        <v>191910567.5176</v>
+        <v>531771831.1712</v>
       </c>
       <c r="G35" t="n">
-        <v>37456630.596</v>
+        <v>132723081.339</v>
       </c>
       <c r="H35" t="n">
-        <v>47977660</v>
+        <v>132947876</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C36" t="n">
+        <v>123190.456</v>
+      </c>
+      <c r="D36" t="n">
+        <v>27919.701</v>
+      </c>
+      <c r="E36" t="n">
+        <v>26830.7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>694026961.3224</v>
+      </c>
+      <c r="G36" t="n">
+        <v>167033674.015</v>
+      </c>
+      <c r="H36" t="n">
+        <v>162243534</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C37" t="n">
+        <v>120126.94</v>
+      </c>
+      <c r="D37" t="n">
+        <v>27217.793</v>
+      </c>
+      <c r="E37" t="n">
+        <v>27197.37</v>
+      </c>
+      <c r="F37" t="n">
+        <v>740738277.8382</v>
+      </c>
+      <c r="G37" t="n">
+        <v>177813277.45</v>
+      </c>
+      <c r="H37" t="n">
+        <v>177097530</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C38" t="n">
+        <v>84254.3057</v>
+      </c>
+      <c r="D38" t="n">
+        <v>26823.903</v>
+      </c>
+      <c r="E38" t="n">
+        <v>26859.11</v>
+      </c>
+      <c r="F38" t="n">
+        <v>625028159.5993</v>
+      </c>
+      <c r="G38" t="n">
+        <v>203583873.108</v>
+      </c>
+      <c r="H38" t="n">
+        <v>203839780</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C39" t="n">
+        <v>90884.2487</v>
+      </c>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39" t="n">
+        <v>595783690.3707</v>
+      </c>
+      <c r="G39"/>
+      <c r="H39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C40"/>
+      <c r="D40" t="n">
+        <v>14686</v>
+      </c>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C41"/>
+      <c r="D41" t="n">
+        <v>15864</v>
+      </c>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C42" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15687</v>
+      </c>
+      <c r="E42"/>
+      <c r="F42" t="n">
+        <v>121491789</v>
+      </c>
+      <c r="G42"/>
+      <c r="H42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C43" t="n">
+        <v>56684</v>
+      </c>
+      <c r="D43" t="n">
+        <v>14825</v>
+      </c>
+      <c r="E43"/>
+      <c r="F43" t="n">
+        <v>105978523.82</v>
+      </c>
+      <c r="G43"/>
+      <c r="H43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C44" t="n">
+        <v>54548</v>
+      </c>
+      <c r="D44" t="n">
+        <v>14245</v>
+      </c>
+      <c r="E44" t="n">
+        <v>14244</v>
+      </c>
+      <c r="F44" t="n">
+        <v>108657760.98</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33505067.816</v>
+      </c>
+      <c r="H44" t="n">
+        <v>28073000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C45" t="n">
+        <v>62036</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15584</v>
+      </c>
+      <c r="E45" t="n">
+        <v>15866</v>
+      </c>
+      <c r="F45" t="n">
+        <v>121172781.7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>37838329.034</v>
+      </c>
+      <c r="H45" t="n">
+        <v>30688000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C46" t="n">
+        <v>58232</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15133</v>
+      </c>
+      <c r="E46" t="n">
+        <v>15133</v>
+      </c>
+      <c r="F46" t="n">
+        <v>119538390.84</v>
+      </c>
+      <c r="G46" t="n">
+        <v>35429471.286</v>
+      </c>
+      <c r="H46" t="n">
+        <v>30568000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C47" t="n">
+        <v>57532</v>
+      </c>
+      <c r="D47" t="n">
+        <v>14918</v>
+      </c>
+      <c r="E47" t="n">
+        <v>14918</v>
+      </c>
+      <c r="F47" t="n">
+        <v>102301006.86</v>
+      </c>
+      <c r="G47" t="n">
+        <v>31291772.688</v>
+      </c>
+      <c r="H47" t="n">
+        <v>26140000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C48" t="n">
+        <v>61464</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15326</v>
+      </c>
+      <c r="E48" t="n">
+        <v>15326</v>
+      </c>
+      <c r="F48" t="n">
+        <v>118008732.16</v>
+      </c>
+      <c r="G48" t="n">
+        <v>35210860.762</v>
+      </c>
+      <c r="H48" t="n">
+        <v>30058000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C49" t="n">
+        <v>69348</v>
+      </c>
+      <c r="D49" t="n">
+        <v>17337</v>
+      </c>
+      <c r="E49" t="n">
+        <v>17337</v>
+      </c>
+      <c r="F49" t="n">
+        <v>122534747.36</v>
+      </c>
+      <c r="G49" t="n">
+        <v>30659887.412</v>
+      </c>
+      <c r="H49" t="n">
+        <v>30627000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C50" t="n">
+        <v>66081.2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16247.969</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16510</v>
+      </c>
+      <c r="F50" t="n">
+        <v>61727750.444</v>
+      </c>
+      <c r="G50" t="n">
+        <v>31540606.104</v>
+      </c>
+      <c r="H50" t="n">
+        <v>31773000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C51" t="n">
+        <v>73030.092</v>
+      </c>
+      <c r="D51" t="n">
+        <v>18257.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>18258</v>
+      </c>
+      <c r="F51" t="n">
+        <v>152027931.94</v>
+      </c>
+      <c r="G51" t="n">
+        <v>38791671.268</v>
+      </c>
+      <c r="H51" t="n">
+        <v>38007000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C52" t="n">
+        <v>71601.596</v>
+      </c>
+      <c r="D52" t="n">
+        <v>17852.3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>17899</v>
+      </c>
+      <c r="F52" t="n">
+        <v>155019979.1364</v>
+      </c>
+      <c r="G52" t="n">
+        <v>38447654.32</v>
+      </c>
+      <c r="H52" t="n">
+        <v>38756000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C53" t="n">
+        <v>69260.48</v>
+      </c>
+      <c r="D53" t="n">
+        <v>17283.305</v>
+      </c>
+      <c r="E53" t="n">
+        <v>17315.12</v>
+      </c>
+      <c r="F53" t="n">
+        <v>143941353.3624</v>
+      </c>
+      <c r="G53" t="n">
+        <v>36041258.536</v>
+      </c>
+      <c r="H53" t="n">
+        <v>35985337</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C54" t="n">
+        <v>73540.472</v>
+      </c>
+      <c r="D54" t="n">
+        <v>18435.87</v>
+      </c>
+      <c r="E54" t="n">
+        <v>22209.728</v>
+      </c>
+      <c r="F54" t="n">
+        <v>139367549.7104</v>
+      </c>
+      <c r="G54" t="n">
+        <v>35610954.217</v>
+      </c>
+      <c r="H54" t="n">
+        <v>41354066</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C55" t="n">
+        <v>71822.516</v>
+      </c>
+      <c r="D55" t="n">
+        <v>18024.757</v>
+      </c>
+      <c r="E55" t="n">
+        <v>17955.629</v>
+      </c>
+      <c r="F55" t="n">
+        <v>155082427.8898</v>
+      </c>
+      <c r="G55" t="n">
+        <v>38483581.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>38770609</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C56" t="n">
+        <v>74827.296</v>
+      </c>
+      <c r="D56" t="n">
+        <v>18557.112</v>
+      </c>
+      <c r="E56" t="n">
+        <v>18706.84</v>
+      </c>
+      <c r="F56" t="n">
+        <v>213208582.5488</v>
+      </c>
+      <c r="G56" t="n">
+        <v>54304484.25</v>
+      </c>
+      <c r="H56" t="n">
+        <v>53302146</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C57" t="n">
+        <v>71394.22</v>
+      </c>
+      <c r="D57" t="n">
+        <v>17785.024</v>
+      </c>
+      <c r="E57" t="n">
+        <v>17848.56</v>
+      </c>
+      <c r="F57" t="n">
+        <v>237492371.82</v>
+      </c>
+      <c r="G57" t="n">
+        <v>61300859.004</v>
+      </c>
+      <c r="H57" t="n">
+        <v>59373100</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C58" t="n">
+        <v>77942.236</v>
+      </c>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58" t="n">
+        <v>238497122.827</v>
+      </c>
+      <c r="G58"/>
+      <c r="H58"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C59"/>
+      <c r="D59" t="n">
+        <v>45753</v>
+      </c>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C60"/>
+      <c r="D60" t="n">
+        <v>57041</v>
+      </c>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C61" t="n">
+        <v>186485.6</v>
+      </c>
+      <c r="D61" t="n">
+        <v>47095.7</v>
+      </c>
+      <c r="E61"/>
+      <c r="F61" t="n">
+        <v>386403109.08</v>
+      </c>
+      <c r="G61"/>
+      <c r="H61"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C62" t="n">
+        <v>317910.2</v>
+      </c>
+      <c r="D62" t="n">
+        <v>55840.6</v>
+      </c>
+      <c r="E62"/>
+      <c r="F62" t="n">
+        <v>455754016.68</v>
+      </c>
+      <c r="G62"/>
+      <c r="H62"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C63" t="n">
+        <v>387831.2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>67140.1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>67145</v>
+      </c>
+      <c r="F63" t="n">
+        <v>572179390.96</v>
+      </c>
+      <c r="G63" t="n">
+        <v>128970349.398</v>
+      </c>
+      <c r="H63" t="n">
+        <v>109001000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C64" t="n">
+        <v>254159.4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>43994.9</v>
+      </c>
+      <c r="E64" t="n">
+        <v>43840</v>
+      </c>
+      <c r="F64" t="n">
+        <v>404759470</v>
+      </c>
+      <c r="G64" t="n">
+        <v>97632285.168</v>
+      </c>
+      <c r="H64" t="n">
+        <v>75218000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C65" t="n">
+        <v>269256.4</v>
+      </c>
+      <c r="D65" t="n">
+        <v>46324.4</v>
+      </c>
+      <c r="E65" t="n">
+        <v>46074</v>
+      </c>
+      <c r="F65" t="n">
+        <v>505077040</v>
+      </c>
+      <c r="G65" t="n">
+        <v>108515379.698</v>
+      </c>
+      <c r="H65" t="n">
+        <v>90649000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C66" t="n">
+        <v>186421.44</v>
+      </c>
+      <c r="D66" t="n">
+        <v>46772</v>
+      </c>
+      <c r="E66" t="n">
+        <v>46705</v>
+      </c>
+      <c r="F66" t="n">
+        <v>440602465.96</v>
+      </c>
+      <c r="G66" t="n">
+        <v>132913406.318</v>
+      </c>
+      <c r="H66" t="n">
+        <v>110901000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C67" t="n">
+        <v>252356.08</v>
+      </c>
+      <c r="D67" t="n">
+        <v>63206</v>
+      </c>
+      <c r="E67" t="n">
+        <v>63289</v>
+      </c>
+      <c r="F67" t="n">
+        <v>392342251.04</v>
+      </c>
+      <c r="G67" t="n">
+        <v>118419178.24</v>
+      </c>
+      <c r="H67" t="n">
+        <v>99533000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C68" t="n">
+        <v>248817.16</v>
+      </c>
+      <c r="D68" t="n">
+        <v>62357</v>
+      </c>
+      <c r="E68" t="n">
+        <v>62435</v>
+      </c>
+      <c r="F68" t="n">
+        <v>378726747.52</v>
+      </c>
+      <c r="G68" t="n">
+        <v>104715679.442</v>
+      </c>
+      <c r="H68" t="n">
+        <v>96342000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C69" t="n">
+        <v>247053.76</v>
+      </c>
+      <c r="D69" t="n">
+        <v>61867</v>
+      </c>
+      <c r="E69" t="n">
+        <v>61874</v>
+      </c>
+      <c r="F69" t="n">
+        <v>342075517.48</v>
+      </c>
+      <c r="G69" t="n">
+        <v>86414406.832</v>
+      </c>
+      <c r="H69" t="n">
+        <v>86338000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C70" t="n">
+        <v>204122</v>
+      </c>
+      <c r="D70" t="n">
+        <v>51460</v>
+      </c>
+      <c r="E70" t="n">
+        <v>51140</v>
+      </c>
+      <c r="F70" t="n">
+        <v>371074664.752</v>
+      </c>
+      <c r="G70" t="n">
+        <v>95725363.755</v>
+      </c>
+      <c r="H70" t="n">
+        <v>93587000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C71" t="n">
+        <v>212016.4</v>
+      </c>
+      <c r="D71" t="n">
+        <v>53542</v>
+      </c>
+      <c r="E71" t="n">
+        <v>53004</v>
+      </c>
+      <c r="F71" t="n">
+        <v>382203365.6</v>
+      </c>
+      <c r="G71" t="n">
+        <v>99719527.984</v>
+      </c>
+      <c r="H71" t="n">
+        <v>95551000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C72" t="n">
+        <v>125441.19</v>
+      </c>
+      <c r="D72" t="n">
+        <v>45987</v>
+      </c>
+      <c r="E72" t="n">
+        <v>46340</v>
+      </c>
+      <c r="F72" t="n">
+        <v>185043130.59</v>
+      </c>
+      <c r="G72" t="n">
+        <v>95869742.062</v>
+      </c>
+      <c r="H72" t="n">
+        <v>84052015</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C73" t="n">
+        <v>108142.96</v>
+      </c>
+      <c r="D73" t="n">
+        <v>40052</v>
+      </c>
+      <c r="E73" t="n">
+        <v>40167.6</v>
+      </c>
+      <c r="F73" t="n">
+        <v>187781438.5924</v>
+      </c>
+      <c r="G73" t="n">
+        <v>92516963.719</v>
+      </c>
+      <c r="H73" t="n">
+        <v>85509274</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C74" t="n">
+        <v>109753.75</v>
+      </c>
+      <c r="D74" t="n">
+        <v>40742</v>
+      </c>
+      <c r="E74" t="n">
+        <v>40526.915</v>
+      </c>
+      <c r="F74" t="n">
+        <v>246230686.5765</v>
+      </c>
+      <c r="G74" t="n">
+        <v>105762551.635</v>
+      </c>
+      <c r="H74" t="n">
+        <v>106793430</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C75" t="n">
+        <v>101701.37</v>
+      </c>
+      <c r="D75" t="n">
+        <v>38477</v>
+      </c>
+      <c r="E75" t="n">
+        <v>37893.79</v>
+      </c>
+      <c r="F75" t="n">
+        <v>227145371.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>109912830.2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>110689319</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C76" t="n">
+        <v>109417.1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>41670.7</v>
+      </c>
+      <c r="E76" t="n">
+        <v>41220.7</v>
+      </c>
+      <c r="F76" t="n">
+        <v>236842499.096</v>
+      </c>
+      <c r="G76" t="n">
+        <v>119195116.656</v>
+      </c>
+      <c r="H76" t="n">
+        <v>116711880</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C77" t="n">
+        <v>83823.6</v>
+      </c>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77" t="n">
+        <v>194350336.8082</v>
+      </c>
+      <c r="G77"/>
+      <c r="H77"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
         <v>12</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B78" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C78"/>
+      <c r="D78" t="n">
+        <v>8088</v>
+      </c>
+      <c r="E78"/>
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="H78"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C79"/>
+      <c r="D79" t="n">
+        <v>10312</v>
+      </c>
+      <c r="E79"/>
+      <c r="F79"/>
+      <c r="G79"/>
+      <c r="H79"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C80" t="n">
+        <v>49984</v>
+      </c>
+      <c r="D80" t="n">
+        <v>12532</v>
+      </c>
+      <c r="E80"/>
+      <c r="F80" t="n">
+        <v>72525714.32</v>
+      </c>
+      <c r="G80"/>
+      <c r="H80"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C81" t="n">
+        <v>52524</v>
+      </c>
+      <c r="D81" t="n">
+        <v>13131</v>
+      </c>
+      <c r="E81"/>
+      <c r="F81" t="n">
+        <v>67959809.96</v>
+      </c>
+      <c r="G81"/>
+      <c r="H81"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C82" t="n">
+        <v>35125.72</v>
+      </c>
+      <c r="D82" t="n">
+        <v>8981.32</v>
+      </c>
+      <c r="E82" t="n">
+        <v>8945</v>
+      </c>
+      <c r="F82" t="n">
+        <v>22420595.38</v>
+      </c>
+      <c r="G82" t="n">
+        <v>23694791.34</v>
+      </c>
+      <c r="H82" t="n">
+        <v>11647000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C83" t="n">
+        <v>33415.7</v>
+      </c>
+      <c r="D83" t="n">
+        <v>8353.27</v>
+      </c>
+      <c r="E83" t="n">
+        <v>8458</v>
+      </c>
+      <c r="F83" t="n">
+        <v>63564018.56</v>
+      </c>
+      <c r="G83" t="n">
+        <v>19929946.168</v>
+      </c>
+      <c r="H83" t="n">
+        <v>16124000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C84" t="n">
+        <v>40037.14</v>
+      </c>
+      <c r="D84" t="n">
+        <v>10004</v>
+      </c>
+      <c r="E84" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F84" t="n">
+        <v>72607995.26</v>
+      </c>
+      <c r="G84" t="n">
+        <v>21030534.998</v>
+      </c>
+      <c r="H84" t="n">
+        <v>18146000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>12</v>
+      </c>
+      <c r="B85" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C85" t="n">
+        <v>40587.15</v>
+      </c>
+      <c r="D85" t="n">
+        <v>10146</v>
+      </c>
+      <c r="E85" t="n">
+        <v>10146</v>
+      </c>
+      <c r="F85" t="n">
+        <v>82580565.6</v>
+      </c>
+      <c r="G85" t="n">
+        <v>24731614.182</v>
+      </c>
+      <c r="H85" t="n">
+        <v>20646000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>12</v>
+      </c>
+      <c r="B86" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C86" t="n">
+        <v>42707.86</v>
+      </c>
+      <c r="D86" t="n">
+        <v>10679.98</v>
+      </c>
+      <c r="E86" t="n">
+        <v>10679</v>
+      </c>
+      <c r="F86" t="n">
+        <v>77109693.65</v>
+      </c>
+      <c r="G86" t="n">
+        <v>23007097.52</v>
+      </c>
+      <c r="H86" t="n">
+        <v>19190000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B87" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C87" t="n">
+        <v>44063.08</v>
+      </c>
+      <c r="D87" t="n">
+        <v>11041.748</v>
+      </c>
+      <c r="E87" t="n">
+        <v>11037</v>
+      </c>
+      <c r="F87" t="n">
+        <v>87090761.01</v>
+      </c>
+      <c r="G87" t="n">
+        <v>21921140.032</v>
+      </c>
+      <c r="H87" t="n">
+        <v>21886000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C88" t="n">
+        <v>50341.916</v>
+      </c>
+      <c r="D88" t="n">
+        <v>12574.03</v>
+      </c>
+      <c r="E88" t="n">
+        <v>12605</v>
+      </c>
+      <c r="F88" t="n">
+        <v>107814223.1216</v>
+      </c>
+      <c r="G88" t="n">
+        <v>27696158.072</v>
+      </c>
+      <c r="H88" t="n">
+        <v>27066000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>12</v>
+      </c>
+      <c r="B89" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C89" t="n">
+        <v>51192.16</v>
+      </c>
+      <c r="D89" t="n">
+        <v>12798.2</v>
+      </c>
+      <c r="E89" t="n">
+        <v>12796</v>
+      </c>
+      <c r="F89" t="n">
+        <v>131161678.73</v>
+      </c>
+      <c r="G89" t="n">
+        <v>32828552.99</v>
+      </c>
+      <c r="H89" t="n">
+        <v>32792000</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C90" t="n">
+        <v>49193.8</v>
+      </c>
+      <c r="D90" t="n">
+        <v>12298.45</v>
+      </c>
+      <c r="E90" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F90" t="n">
+        <v>134230777.8394</v>
+      </c>
+      <c r="G90" t="n">
+        <v>30648544.048</v>
+      </c>
+      <c r="H90" t="n">
+        <v>33559000</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C91" t="n">
+        <v>50512</v>
+      </c>
+      <c r="D91" t="n">
+        <v>12847.787</v>
+      </c>
+      <c r="E91" t="n">
+        <v>12628</v>
+      </c>
+      <c r="F91" t="n">
+        <v>149937833.1108</v>
+      </c>
+      <c r="G91" t="n">
+        <v>31861870.298</v>
+      </c>
+      <c r="H91" t="n">
+        <v>37484459</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C92" t="n">
+        <v>48600</v>
+      </c>
+      <c r="D92" t="n">
+        <v>12371</v>
+      </c>
+      <c r="E92" t="n">
+        <v>12078</v>
+      </c>
+      <c r="F92" t="n">
+        <v>155951470.8884</v>
+      </c>
+      <c r="G92" t="n">
+        <v>39335531.998</v>
+      </c>
+      <c r="H92" t="n">
+        <v>38789821</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C93" t="n">
+        <v>46856</v>
+      </c>
+      <c r="D93" t="n">
+        <v>11714</v>
+      </c>
+      <c r="E93" t="n">
+        <v>11714</v>
+      </c>
+      <c r="F93" t="n">
+        <v>143440009.0512</v>
+      </c>
+      <c r="G93" t="n">
+        <v>36587678.66</v>
+      </c>
+      <c r="H93" t="n">
+        <v>35860002</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C94" t="n">
+        <v>44848</v>
+      </c>
+      <c r="D94" t="n">
+        <v>11210.78</v>
+      </c>
+      <c r="E94" t="n">
+        <v>11212</v>
+      </c>
+      <c r="F94" t="n">
+        <v>164806846.6648</v>
+      </c>
+      <c r="G94" t="n">
+        <v>36065958.65</v>
+      </c>
+      <c r="H94" t="n">
+        <v>41201711</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C95" t="n">
+        <v>45048</v>
+      </c>
+      <c r="D95" t="n">
+        <v>11264.3</v>
+      </c>
+      <c r="E95" t="n">
+        <v>11262</v>
+      </c>
+      <c r="F95" t="n">
+        <v>191910567.5176</v>
+      </c>
+      <c r="G95" t="n">
+        <v>37456630.596</v>
+      </c>
+      <c r="H95" t="n">
+        <v>47977660</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" t="n">
         <v>2024</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C96" t="n">
         <v>40216</v>
       </c>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36" t="n">
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96" t="n">
         <v>175173883.0176</v>
       </c>
-      <c r="G36"/>
-      <c r="H36"/>
+      <c r="G96"/>
+      <c r="H96"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1343,804 +2713,2154 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>2018</v>
+        <v>2006</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="n">
-        <v>111</v>
-      </c>
-      <c r="E2" t="n">
-        <v>111</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="E2"/>
       <c r="F2"/>
-      <c r="G2" t="n">
-        <v>842599.936</v>
-      </c>
-      <c r="H2" t="n">
-        <v>841000</v>
-      </c>
+      <c r="G2"/>
+      <c r="H2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>2019</v>
+        <v>2007</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="n">
-        <v>86</v>
-      </c>
-      <c r="E3" t="n">
-        <v>86</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="E3"/>
       <c r="F3"/>
-      <c r="G3" t="n">
-        <v>538193.24</v>
-      </c>
-      <c r="H3" t="n">
-        <v>538347</v>
-      </c>
+      <c r="G3"/>
+      <c r="H3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C4"/>
+        <v>2008</v>
+      </c>
+      <c r="C4" t="n">
+        <v>252</v>
+      </c>
       <c r="D4" t="n">
-        <v>209</v>
-      </c>
-      <c r="E4" t="n">
-        <v>209</v>
-      </c>
-      <c r="F4"/>
-      <c r="G4" t="n">
-        <v>1396408.512</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1394030</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4" t="n">
+        <v>1335534</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C5"/>
+        <v>2009</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1152</v>
+      </c>
       <c r="D5" t="n">
-        <v>223</v>
-      </c>
-      <c r="E5" t="n">
-        <v>223</v>
-      </c>
-      <c r="F5"/>
-      <c r="G5" t="n">
-        <v>1446424.525</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1447320</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5" t="n">
+        <v>8434360</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="n">
-        <v>243</v>
-      </c>
-      <c r="E6" t="n">
-        <v>243</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="n">
-        <v>1740569.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1739960</v>
-      </c>
+        <v>4016295.712</v>
+      </c>
+      <c r="H6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
+        <v>2011</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="n">
-        <v>261</v>
-      </c>
-      <c r="E7" t="n">
-        <v>261</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="E7"/>
       <c r="F7"/>
       <c r="G7" t="n">
-        <v>1830556.728</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1832170</v>
-      </c>
+        <v>582872.4</v>
+      </c>
+      <c r="H7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C8" t="n">
-        <v>5797.66</v>
-      </c>
+        <v>2012</v>
+      </c>
+      <c r="C8"/>
       <c r="D8" t="n">
-        <v>2898.83</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2529</v>
-      </c>
-      <c r="F8" t="n">
-        <v>13482128.0116</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8"/>
       <c r="G8" t="n">
-        <v>6753526.272</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5378000</v>
-      </c>
+        <v>2535975.706</v>
+      </c>
+      <c r="H8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C9" t="n">
-        <v>6200.93</v>
-      </c>
+        <v>2013</v>
+      </c>
+      <c r="C9"/>
       <c r="D9" t="n">
-        <v>3100.45</v>
+        <v>212</v>
       </c>
       <c r="E9" t="n">
-        <v>2728.455</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14195155.8356</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F9"/>
       <c r="G9" t="n">
-        <v>7099316.959</v>
+        <v>1208540.19</v>
       </c>
       <c r="H9" t="n">
-        <v>5727432</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C10" t="n">
-        <v>5556.8</v>
+        <v>428</v>
       </c>
       <c r="D10" t="n">
-        <v>2731.98</v>
+        <v>214</v>
       </c>
       <c r="E10" t="n">
-        <v>2387.53</v>
+        <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>12407013.4238</v>
+        <v>1931358.56</v>
       </c>
       <c r="G10" t="n">
-        <v>6028455.904</v>
+        <v>1219265.872</v>
       </c>
       <c r="H10" t="n">
-        <v>4677074</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C11" t="n">
-        <v>8280.8</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>4142.9</v>
+        <v>82</v>
       </c>
       <c r="E11" t="n">
-        <v>3690.5</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>18387732.6308</v>
+        <v>332992</v>
       </c>
       <c r="G11" t="n">
-        <v>9204773.435</v>
+        <v>540421.574</v>
       </c>
       <c r="H11" t="n">
-        <v>7547190</v>
+        <v>320000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8234.44</v>
-      </c>
+        <v>2016</v>
+      </c>
+      <c r="C12"/>
       <c r="D12" t="n">
-        <v>4117.226</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
-        <v>3693.18</v>
-      </c>
-      <c r="F12" t="n">
-        <v>21216948.7878</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F12"/>
       <c r="G12" t="n">
-        <v>10606048.9</v>
+        <v>440281.448</v>
       </c>
       <c r="H12" t="n">
-        <v>8769907</v>
+        <v>452000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C13" t="n">
-        <v>7353.1258</v>
-      </c>
+        <v>2017</v>
+      </c>
+      <c r="C13"/>
       <c r="D13" t="n">
-        <v>3675.566</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
-        <v>3238.29</v>
-      </c>
-      <c r="F13" t="n">
-        <v>26987699.483</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F13"/>
       <c r="G13" t="n">
-        <v>13475102.256</v>
+        <v>686889.252</v>
       </c>
       <c r="H13" t="n">
-        <v>11394220</v>
+        <v>683000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C14" t="n">
-        <v>8863.1496</v>
-      </c>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14" t="n">
-        <v>28954964.5582</v>
-      </c>
-      <c r="G14"/>
-      <c r="H14"/>
+        <v>2018</v>
+      </c>
+      <c r="C14"/>
+      <c r="D14" t="n">
+        <v>111</v>
+      </c>
+      <c r="E14" t="n">
+        <v>111</v>
+      </c>
+      <c r="F14"/>
+      <c r="G14" t="n">
+        <v>842599.936</v>
+      </c>
+      <c r="H14" t="n">
+        <v>841000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C15" t="n">
-        <v>35800.798</v>
-      </c>
+        <v>2019</v>
+      </c>
+      <c r="C15"/>
       <c r="D15" t="n">
-        <v>17852.3</v>
+        <v>86</v>
       </c>
       <c r="E15" t="n">
-        <v>17827</v>
-      </c>
-      <c r="F15" t="n">
-        <v>77509989.5682</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="F15"/>
       <c r="G15" t="n">
-        <v>38447654.32</v>
+        <v>538193.24</v>
       </c>
       <c r="H15" t="n">
-        <v>38467000</v>
+        <v>538347</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C16" t="n">
-        <v>34630.24</v>
-      </c>
+        <v>2020</v>
+      </c>
+      <c r="C16"/>
       <c r="D16" t="n">
-        <v>17283.305</v>
+        <v>209</v>
       </c>
       <c r="E16" t="n">
-        <v>17238.745</v>
-      </c>
-      <c r="F16" t="n">
-        <v>71970676.6812</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="F16"/>
       <c r="G16" t="n">
-        <v>36041258.536</v>
+        <v>1396408.512</v>
       </c>
       <c r="H16" t="n">
-        <v>35674249</v>
+        <v>1394030</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B17" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C17" t="n">
-        <v>36770.236</v>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="C17"/>
       <c r="D17" t="n">
-        <v>18435.87</v>
+        <v>223</v>
       </c>
       <c r="E17" t="n">
-        <v>22114.773</v>
-      </c>
-      <c r="F17" t="n">
-        <v>69683774.8552</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="F17"/>
       <c r="G17" t="n">
-        <v>35610954.217</v>
+        <v>1446424.525</v>
       </c>
       <c r="H17" t="n">
-        <v>41005875</v>
+        <v>1447320</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B18" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C18" t="n">
-        <v>35911.258</v>
-      </c>
+        <v>2022</v>
+      </c>
+      <c r="C18"/>
       <c r="D18" t="n">
-        <v>18024.757</v>
+        <v>243</v>
       </c>
       <c r="E18" t="n">
-        <v>17882.129</v>
-      </c>
-      <c r="F18" t="n">
-        <v>77541213.9449</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="F18"/>
       <c r="G18" t="n">
-        <v>38483581.5</v>
+        <v>1740569.1</v>
       </c>
       <c r="H18" t="n">
-        <v>38258905</v>
+        <v>1739960</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B19" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C19" t="n">
-        <v>37413.648</v>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C19"/>
       <c r="D19" t="n">
-        <v>18557.112</v>
+        <v>261</v>
       </c>
       <c r="E19" t="n">
-        <v>18645.62</v>
-      </c>
-      <c r="F19" t="n">
-        <v>106604291.2744</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="F19"/>
       <c r="G19" t="n">
-        <v>54304484.25</v>
+        <v>1830556.728</v>
       </c>
       <c r="H19" t="n">
-        <v>53006770</v>
+        <v>1832170</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C20" t="n">
-        <v>35697.11</v>
-      </c>
+        <v>2006</v>
+      </c>
+      <c r="C20"/>
       <c r="D20" t="n">
-        <v>17785.024</v>
-      </c>
-      <c r="E20" t="n">
-        <v>17773.01</v>
-      </c>
-      <c r="F20" t="n">
-        <v>118746185.91</v>
-      </c>
-      <c r="G20" t="n">
-        <v>61300859.004</v>
-      </c>
-      <c r="H20" t="n">
-        <v>58819110</v>
-      </c>
+        <v>5087</v>
+      </c>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C21" t="n">
-        <v>38971.118</v>
-      </c>
-      <c r="D21"/>
+        <v>2007</v>
+      </c>
+      <c r="C21"/>
+      <c r="D21" t="n">
+        <v>4395</v>
+      </c>
       <c r="E21"/>
-      <c r="F21" t="n">
-        <v>119248561.4135</v>
-      </c>
+      <c r="F21"/>
       <c r="G21"/>
       <c r="H21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B22" t="n">
-        <v>2018</v>
+        <v>2008</v>
       </c>
       <c r="C22" t="n">
-        <v>9822</v>
+        <v>10350</v>
       </c>
       <c r="D22" t="n">
-        <v>5015</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4620</v>
-      </c>
-      <c r="F22" t="n">
-        <v>59374000</v>
-      </c>
-      <c r="G22" t="n">
-        <v>32393084.416</v>
-      </c>
-      <c r="H22" t="n">
-        <v>26527000</v>
-      </c>
+        <v>4458</v>
+      </c>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B23" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C23"/>
+        <v>2009</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10132</v>
+      </c>
       <c r="D23" t="n">
-        <v>5310</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5220</v>
-      </c>
-      <c r="F23"/>
-      <c r="G23" t="n">
-        <v>29441291.996</v>
-      </c>
-      <c r="H23" t="n">
-        <v>27519909</v>
-      </c>
+        <v>5066</v>
+      </c>
+      <c r="E23"/>
+      <c r="F23" t="n">
+        <v>20250842.24</v>
+      </c>
+      <c r="G23"/>
+      <c r="H23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B24" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C24"/>
+        <v>2010</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10116</v>
+      </c>
       <c r="D24" t="n">
-        <v>4860</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4805</v>
-      </c>
-      <c r="F24"/>
+        <v>5048</v>
+      </c>
+      <c r="E24"/>
+      <c r="F24" t="n">
+        <v>23539531.71</v>
+      </c>
       <c r="G24" t="n">
-        <v>27296888.977</v>
-      </c>
-      <c r="H24" t="n">
-        <v>26467883</v>
-      </c>
+        <v>13885658.6</v>
+      </c>
+      <c r="H24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B25" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C25"/>
+        <v>2011</v>
+      </c>
+      <c r="C25" t="n">
+        <v>12566</v>
+      </c>
       <c r="D25" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E25" t="n">
-        <v>4400</v>
-      </c>
-      <c r="F25"/>
+        <v>6283</v>
+      </c>
+      <c r="E25"/>
+      <c r="F25" t="n">
+        <v>24279981.32</v>
+      </c>
       <c r="G25" t="n">
-        <v>26569863.125</v>
-      </c>
-      <c r="H25" t="n">
-        <v>23425000</v>
-      </c>
+        <v>15222446.052</v>
+      </c>
+      <c r="H25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C26"/>
+        <v>2012</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8427.7</v>
+      </c>
       <c r="D26" t="n">
-        <v>4670</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4400</v>
-      </c>
-      <c r="F26"/>
+        <v>4214</v>
+      </c>
+      <c r="E26"/>
+      <c r="F26" t="n">
+        <v>15808741.28</v>
+      </c>
       <c r="G26" t="n">
-        <v>25608541.05</v>
-      </c>
-      <c r="H26" t="n">
-        <v>29900800</v>
-      </c>
+        <v>9193050.504</v>
+      </c>
+      <c r="H26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B27" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C27"/>
+        <v>2013</v>
+      </c>
+      <c r="C27" t="n">
+        <v>6469.99</v>
+      </c>
       <c r="D27" t="n">
-        <v>4770</v>
+        <v>3235</v>
       </c>
       <c r="E27" t="n">
-        <v>2650</v>
-      </c>
-      <c r="F27"/>
+        <v>2885</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13173116.55</v>
+      </c>
       <c r="G27" t="n">
-        <v>33820369.968</v>
+        <v>7891551.096</v>
       </c>
       <c r="H27" t="n">
-        <v>6651310</v>
+        <v>5446000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B28" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
+        <v>2014</v>
+      </c>
+      <c r="C28" t="n">
+        <v>7615.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3808</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3430</v>
+      </c>
+      <c r="F28" t="n">
+        <v>13707402.62</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8211637.522</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5721000</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B29" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C29" t="n">
-        <v>24596.9</v>
+        <v>9664.4</v>
       </c>
       <c r="D29" t="n">
-        <v>12298.45</v>
+        <v>4831.91</v>
       </c>
       <c r="E29" t="n">
-        <v>9826</v>
+        <v>4154</v>
       </c>
       <c r="F29" t="n">
-        <v>67115388.9197</v>
+        <v>16644577.54</v>
       </c>
       <c r="G29" t="n">
-        <v>30648544.048</v>
+        <v>8333331.754</v>
       </c>
       <c r="H29" t="n">
-        <v>24954000</v>
+        <v>6298000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B30" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C30" t="n">
-        <v>25256</v>
+        <v>8068.42</v>
       </c>
       <c r="D30" t="n">
-        <v>12847.787</v>
+        <v>4034.2</v>
       </c>
       <c r="E30" t="n">
-        <v>10091</v>
+        <v>3567</v>
       </c>
       <c r="F30" t="n">
-        <v>74968916.5554</v>
+        <v>15738810.69</v>
       </c>
       <c r="G30" t="n">
-        <v>31861870.298</v>
+        <v>7874438.448</v>
       </c>
       <c r="H30" t="n">
-        <v>27861042</v>
+        <v>6297000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B31" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C31" t="n">
-        <v>24300</v>
+        <v>6544.4</v>
       </c>
       <c r="D31" t="n">
-        <v>12371</v>
+        <v>3272.2</v>
       </c>
       <c r="E31" t="n">
-        <v>9442</v>
+        <v>2877</v>
       </c>
       <c r="F31" t="n">
-        <v>77975735.4442</v>
+        <v>13931118.32</v>
       </c>
       <c r="G31" t="n">
-        <v>39335531.998</v>
+        <v>6961847.459</v>
       </c>
       <c r="H31" t="n">
-        <v>27893432</v>
+        <v>5614000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B32" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C32" t="n">
-        <v>23428</v>
+        <v>5797.66</v>
       </c>
       <c r="D32" t="n">
-        <v>11714</v>
+        <v>2898.83</v>
       </c>
       <c r="E32" t="n">
-        <v>8967</v>
+        <v>2529</v>
       </c>
       <c r="F32" t="n">
-        <v>71720004.5256</v>
+        <v>13482128.0116</v>
       </c>
       <c r="G32" t="n">
-        <v>36587678.66</v>
+        <v>6753526.272</v>
       </c>
       <c r="H32" t="n">
-        <v>24696739</v>
+        <v>5378000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B33" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C33" t="n">
-        <v>22424</v>
+        <v>6200.93</v>
       </c>
       <c r="D33" t="n">
-        <v>11210.78</v>
+        <v>3100.45</v>
       </c>
       <c r="E33" t="n">
-        <v>8105</v>
+        <v>2728.455</v>
       </c>
       <c r="F33" t="n">
-        <v>82403423.3324</v>
+        <v>14195155.8356</v>
       </c>
       <c r="G33" t="n">
-        <v>36065958.65</v>
+        <v>7099316.959</v>
       </c>
       <c r="H33" t="n">
-        <v>24820229</v>
+        <v>5727432</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B34" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C34" t="n">
-        <v>22524</v>
+        <v>5556.8</v>
       </c>
       <c r="D34" t="n">
-        <v>11264.3</v>
+        <v>2731.98</v>
       </c>
       <c r="E34" t="n">
-        <v>7735</v>
+        <v>2387.53</v>
       </c>
       <c r="F34" t="n">
-        <v>95955283.7588</v>
+        <v>12407013.4238</v>
       </c>
       <c r="G34" t="n">
-        <v>37456630.596</v>
+        <v>6028455.904</v>
       </c>
       <c r="H34" t="n">
-        <v>26587640</v>
+        <v>4677074</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8280.8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4142.9</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3690.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>18387732.6308</v>
+      </c>
+      <c r="G35" t="n">
+        <v>9204773.435</v>
+      </c>
+      <c r="H35" t="n">
+        <v>7547190</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8234.44</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4117.226</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3693.18</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21216948.7878</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10606048.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8769907</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C37" t="n">
+        <v>7353.1258</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3675.566</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3238.29</v>
+      </c>
+      <c r="F37" t="n">
+        <v>26987699.483</v>
+      </c>
+      <c r="G37" t="n">
+        <v>13475102.256</v>
+      </c>
+      <c r="H37" t="n">
+        <v>11394220</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8863.1496</v>
+      </c>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38" t="n">
+        <v>28954964.5582</v>
+      </c>
+      <c r="G38"/>
+      <c r="H38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C39"/>
+      <c r="D39" t="n">
+        <v>14686</v>
+      </c>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C40"/>
+      <c r="D40" t="n">
+        <v>15864</v>
+      </c>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C41" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D41" t="n">
+        <v>15687</v>
+      </c>
+      <c r="E41"/>
+      <c r="F41" t="n">
+        <v>60745894.5</v>
+      </c>
+      <c r="G41"/>
+      <c r="H41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C42" t="n">
+        <v>28342</v>
+      </c>
+      <c r="D42" t="n">
+        <v>14825</v>
+      </c>
+      <c r="E42"/>
+      <c r="F42" t="n">
+        <v>52989261.91</v>
+      </c>
+      <c r="G42"/>
+      <c r="H42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C43" t="n">
+        <v>27274</v>
+      </c>
+      <c r="D43" t="n">
+        <v>14245</v>
+      </c>
+      <c r="E43" t="n">
+        <v>14197</v>
+      </c>
+      <c r="F43" t="n">
+        <v>54328880.49</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33505067.816</v>
+      </c>
+      <c r="H43" t="n">
+        <v>27868000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C44" t="n">
+        <v>31018</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15584</v>
+      </c>
+      <c r="E44" t="n">
+        <v>15822</v>
+      </c>
+      <c r="F44" t="n">
+        <v>60586390.85</v>
+      </c>
+      <c r="G44" t="n">
+        <v>37838329.034</v>
+      </c>
+      <c r="H44" t="n">
+        <v>30483000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C45" t="n">
+        <v>29116</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15133</v>
+      </c>
+      <c r="E45" t="n">
+        <v>15088</v>
+      </c>
+      <c r="F45" t="n">
+        <v>59769195.42</v>
+      </c>
+      <c r="G45" t="n">
+        <v>35429471.286</v>
+      </c>
+      <c r="H45" t="n">
+        <v>30322000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C46" t="n">
+        <v>28766</v>
+      </c>
+      <c r="D46" t="n">
+        <v>14918</v>
+      </c>
+      <c r="E46" t="n">
+        <v>14866</v>
+      </c>
+      <c r="F46" t="n">
+        <v>51150503.43</v>
+      </c>
+      <c r="G46" t="n">
+        <v>31291772.688</v>
+      </c>
+      <c r="H46" t="n">
+        <v>25927000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C47" t="n">
+        <v>30732</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15326</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15265</v>
+      </c>
+      <c r="F47" t="n">
+        <v>59004366.08</v>
+      </c>
+      <c r="G47" t="n">
+        <v>35210860.762</v>
+      </c>
+      <c r="H47" t="n">
+        <v>29767000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C48" t="n">
+        <v>34674</v>
+      </c>
+      <c r="D48" t="n">
+        <v>17337</v>
+      </c>
+      <c r="E48" t="n">
+        <v>17295</v>
+      </c>
+      <c r="F48" t="n">
+        <v>61267373.68</v>
+      </c>
+      <c r="G48" t="n">
+        <v>30659887.412</v>
+      </c>
+      <c r="H48" t="n">
+        <v>30433000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C49" t="n">
+        <v>33040.6</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16247.969</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16443</v>
+      </c>
+      <c r="F49" t="n">
+        <v>30863875.222</v>
+      </c>
+      <c r="G49" t="n">
+        <v>31540606.104</v>
+      </c>
+      <c r="H49" t="n">
+        <v>31475000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C50" t="n">
+        <v>36515.046</v>
+      </c>
+      <c r="D50" t="n">
+        <v>18257.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>18204</v>
+      </c>
+      <c r="F50" t="n">
+        <v>76013965.97</v>
+      </c>
+      <c r="G50" t="n">
+        <v>38791671.268</v>
+      </c>
+      <c r="H50" t="n">
+        <v>37739000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C51" t="n">
+        <v>35800.798</v>
+      </c>
+      <c r="D51" t="n">
+        <v>17852.3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>17827</v>
+      </c>
+      <c r="F51" t="n">
+        <v>77509989.5682</v>
+      </c>
+      <c r="G51" t="n">
+        <v>38447654.32</v>
+      </c>
+      <c r="H51" t="n">
+        <v>38467000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C52" t="n">
+        <v>34630.24</v>
+      </c>
+      <c r="D52" t="n">
+        <v>17283.305</v>
+      </c>
+      <c r="E52" t="n">
+        <v>17238.745</v>
+      </c>
+      <c r="F52" t="n">
+        <v>71970676.6812</v>
+      </c>
+      <c r="G52" t="n">
+        <v>36041258.536</v>
+      </c>
+      <c r="H52" t="n">
+        <v>35674249</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C53" t="n">
+        <v>36770.236</v>
+      </c>
+      <c r="D53" t="n">
+        <v>18435.87</v>
+      </c>
+      <c r="E53" t="n">
+        <v>22114.773</v>
+      </c>
+      <c r="F53" t="n">
+        <v>69683774.8552</v>
+      </c>
+      <c r="G53" t="n">
+        <v>35610954.217</v>
+      </c>
+      <c r="H53" t="n">
+        <v>41005875</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C54" t="n">
+        <v>35911.258</v>
+      </c>
+      <c r="D54" t="n">
+        <v>18024.757</v>
+      </c>
+      <c r="E54" t="n">
+        <v>17882.129</v>
+      </c>
+      <c r="F54" t="n">
+        <v>77541213.9449</v>
+      </c>
+      <c r="G54" t="n">
+        <v>38483581.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>38258905</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C55" t="n">
+        <v>37413.648</v>
+      </c>
+      <c r="D55" t="n">
+        <v>18557.112</v>
+      </c>
+      <c r="E55" t="n">
+        <v>18645.62</v>
+      </c>
+      <c r="F55" t="n">
+        <v>106604291.2744</v>
+      </c>
+      <c r="G55" t="n">
+        <v>54304484.25</v>
+      </c>
+      <c r="H55" t="n">
+        <v>53006770</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C56" t="n">
+        <v>35697.11</v>
+      </c>
+      <c r="D56" t="n">
+        <v>17785.024</v>
+      </c>
+      <c r="E56" t="n">
+        <v>17773.01</v>
+      </c>
+      <c r="F56" t="n">
+        <v>118746185.91</v>
+      </c>
+      <c r="G56" t="n">
+        <v>61300859.004</v>
+      </c>
+      <c r="H56" t="n">
+        <v>58819110</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C57" t="n">
+        <v>38971.118</v>
+      </c>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57" t="n">
+        <v>119248561.4135</v>
+      </c>
+      <c r="G57"/>
+      <c r="H57"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C58"/>
+      <c r="D58" t="n">
+        <v>10800</v>
+      </c>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C59"/>
+      <c r="D59" t="n">
+        <v>9630</v>
+      </c>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C60" t="n">
+        <v>17130</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8655</v>
+      </c>
+      <c r="E60"/>
+      <c r="F60" t="n">
+        <v>57130088</v>
+      </c>
+      <c r="G60"/>
+      <c r="H60"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C61" t="n">
+        <v>15454</v>
+      </c>
+      <c r="D61" t="n">
+        <v>7862</v>
+      </c>
+      <c r="E61"/>
+      <c r="F61" t="n">
+        <v>48902959.8</v>
+      </c>
+      <c r="G61"/>
+      <c r="H61"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C62" t="n">
+        <v>12940</v>
+      </c>
+      <c r="D62" t="n">
+        <v>6485</v>
+      </c>
+      <c r="E62" t="n">
+        <v>6570</v>
+      </c>
+      <c r="F62" t="n">
+        <v>62039996</v>
+      </c>
+      <c r="G62" t="n">
+        <v>37051753.464</v>
+      </c>
+      <c r="H62" t="n">
+        <v>32069000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C63" t="n">
+        <v>8160</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4135</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3790</v>
+      </c>
+      <c r="F63" t="n">
+        <v>38999900</v>
+      </c>
+      <c r="G63" t="n">
+        <v>27792338.31</v>
+      </c>
+      <c r="H63" t="n">
+        <v>19559000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C64" t="n">
+        <v>6470</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3385</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3120</v>
+      </c>
+      <c r="F64" t="n">
+        <v>31616000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>21827492.588</v>
+      </c>
+      <c r="H64" t="n">
+        <v>16350000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C65" t="n">
+        <v>12750</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6330</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6135</v>
+      </c>
+      <c r="F65" t="n">
+        <v>64114999.98</v>
+      </c>
+      <c r="G65" t="n">
+        <v>38427642.616</v>
+      </c>
+      <c r="H65" t="n">
+        <v>30223000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C66" t="n">
+        <v>11250</v>
+      </c>
+      <c r="D66" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E66" t="n">
+        <v>5335</v>
+      </c>
+      <c r="F66" t="n">
+        <v>47160000</v>
+      </c>
+      <c r="G66" t="n">
+        <v>27537111.998</v>
+      </c>
+      <c r="H66" t="n">
+        <v>21394000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C67" t="n">
+        <v>10380</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5145</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5030</v>
+      </c>
+      <c r="F67" t="n">
+        <v>47070000.02</v>
+      </c>
+      <c r="G67" t="n">
+        <v>24589180.264</v>
+      </c>
+      <c r="H67" t="n">
+        <v>22260000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C68" t="n">
+        <v>10380</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5115</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4910</v>
+      </c>
+      <c r="F68" t="n">
+        <v>49070000.02</v>
+      </c>
+      <c r="G68" t="n">
+        <v>25446385.928</v>
+      </c>
+      <c r="H68" t="n">
+        <v>22420000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C69" t="n">
+        <v>9522</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4765</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4480</v>
+      </c>
+      <c r="F69" t="n">
+        <v>56329002.02</v>
+      </c>
+      <c r="G69" t="n">
+        <v>30319039.285</v>
+      </c>
+      <c r="H69" t="n">
+        <v>25075000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C70" t="n">
+        <v>9822</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5015</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4620</v>
+      </c>
+      <c r="F70" t="n">
+        <v>59374000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>32393084.416</v>
+      </c>
+      <c r="H70" t="n">
+        <v>26527000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C71"/>
+      <c r="D71" t="n">
+        <v>5310</v>
+      </c>
+      <c r="E71" t="n">
+        <v>5220</v>
+      </c>
+      <c r="F71"/>
+      <c r="G71" t="n">
+        <v>29441291.996</v>
+      </c>
+      <c r="H71" t="n">
+        <v>27519909</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C72"/>
+      <c r="D72" t="n">
+        <v>4860</v>
+      </c>
+      <c r="E72" t="n">
+        <v>4805</v>
+      </c>
+      <c r="F72"/>
+      <c r="G72" t="n">
+        <v>27296888.977</v>
+      </c>
+      <c r="H72" t="n">
+        <v>26467883</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C73"/>
+      <c r="D73" t="n">
+        <v>4820</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4400</v>
+      </c>
+      <c r="F73"/>
+      <c r="G73" t="n">
+        <v>26569863.125</v>
+      </c>
+      <c r="H73" t="n">
+        <v>23425000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C74"/>
+      <c r="D74" t="n">
+        <v>4670</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4400</v>
+      </c>
+      <c r="F74"/>
+      <c r="G74" t="n">
+        <v>25608541.05</v>
+      </c>
+      <c r="H74" t="n">
+        <v>29900800</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C75"/>
+      <c r="D75" t="n">
+        <v>4770</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2650</v>
+      </c>
+      <c r="F75"/>
+      <c r="G75" t="n">
+        <v>33820369.968</v>
+      </c>
+      <c r="H75" t="n">
+        <v>6651310</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C76"/>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76"/>
+      <c r="G76"/>
+      <c r="H76"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
         <v>12</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B77" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C77"/>
+      <c r="D77" t="n">
+        <v>8088</v>
+      </c>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C78"/>
+      <c r="D78" t="n">
+        <v>10312</v>
+      </c>
+      <c r="E78"/>
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="H78"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C79" t="n">
+        <v>24992</v>
+      </c>
+      <c r="D79" t="n">
+        <v>12532</v>
+      </c>
+      <c r="E79"/>
+      <c r="F79" t="n">
+        <v>36262857.16</v>
+      </c>
+      <c r="G79"/>
+      <c r="H79"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C80" t="n">
+        <v>26262</v>
+      </c>
+      <c r="D80" t="n">
+        <v>13131</v>
+      </c>
+      <c r="E80"/>
+      <c r="F80" t="n">
+        <v>33979904.98</v>
+      </c>
+      <c r="G80"/>
+      <c r="H80"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C81" t="n">
+        <v>17562.86</v>
+      </c>
+      <c r="D81" t="n">
+        <v>8981.32</v>
+      </c>
+      <c r="E81" t="n">
+        <v>7545</v>
+      </c>
+      <c r="F81" t="n">
+        <v>11210297.69</v>
+      </c>
+      <c r="G81" t="n">
+        <v>23694791.34</v>
+      </c>
+      <c r="H81" t="n">
+        <v>6661000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C82" t="n">
+        <v>16703.92</v>
+      </c>
+      <c r="D82" t="n">
+        <v>8351.96</v>
+      </c>
+      <c r="E82" t="n">
+        <v>6747</v>
+      </c>
+      <c r="F82" t="n">
+        <v>31776771.61</v>
+      </c>
+      <c r="G82" t="n">
+        <v>19927756.112</v>
+      </c>
+      <c r="H82" t="n">
+        <v>10011000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C83" t="n">
+        <v>19991.04</v>
+      </c>
+      <c r="D83" t="n">
+        <v>9995</v>
+      </c>
+      <c r="E83" t="n">
+        <v>8921</v>
+      </c>
+      <c r="F83" t="n">
+        <v>36270469.72</v>
+      </c>
+      <c r="G83" t="n">
+        <v>21017675.184</v>
+      </c>
+      <c r="H83" t="n">
+        <v>13997000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C84" t="n">
+        <v>20260.8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>10130</v>
+      </c>
+      <c r="E84" t="n">
+        <v>9024</v>
+      </c>
+      <c r="F84" t="n">
+        <v>41237637.4</v>
+      </c>
+      <c r="G84" t="n">
+        <v>24703418.564</v>
+      </c>
+      <c r="H84" t="n">
+        <v>16356000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>12</v>
+      </c>
+      <c r="B85" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C85" t="n">
+        <v>21279.47</v>
+      </c>
+      <c r="D85" t="n">
+        <v>10642.75</v>
+      </c>
+      <c r="E85" t="n">
+        <v>9489</v>
+      </c>
+      <c r="F85" t="n">
+        <v>38324673.32</v>
+      </c>
+      <c r="G85" t="n">
+        <v>22869804.1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>15255000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>12</v>
+      </c>
+      <c r="B86" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C86" t="n">
+        <v>21961.9</v>
+      </c>
+      <c r="D86" t="n">
+        <v>10986.928</v>
+      </c>
+      <c r="E86" t="n">
+        <v>9439</v>
+      </c>
+      <c r="F86" t="n">
+        <v>43444143.72</v>
+      </c>
+      <c r="G86" t="n">
+        <v>21757819.402</v>
+      </c>
+      <c r="H86" t="n">
+        <v>16286000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B87" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C87" t="n">
+        <v>25121.678</v>
+      </c>
+      <c r="D87" t="n">
+        <v>12529.39</v>
+      </c>
+      <c r="E87" t="n">
+        <v>10964</v>
+      </c>
+      <c r="F87" t="n">
+        <v>53835886.9058</v>
+      </c>
+      <c r="G87" t="n">
+        <v>27549411.752</v>
+      </c>
+      <c r="H87" t="n">
+        <v>20070000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C88" t="n">
+        <v>25596.08</v>
+      </c>
+      <c r="D88" t="n">
+        <v>12798.2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>10717</v>
+      </c>
+      <c r="F88" t="n">
+        <v>65580839.365</v>
+      </c>
+      <c r="G88" t="n">
+        <v>32828552.99</v>
+      </c>
+      <c r="H88" t="n">
+        <v>24509000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>12</v>
+      </c>
+      <c r="B89" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C89" t="n">
+        <v>24596.9</v>
+      </c>
+      <c r="D89" t="n">
+        <v>12298.45</v>
+      </c>
+      <c r="E89" t="n">
+        <v>9826</v>
+      </c>
+      <c r="F89" t="n">
+        <v>67115388.9197</v>
+      </c>
+      <c r="G89" t="n">
+        <v>30648544.048</v>
+      </c>
+      <c r="H89" t="n">
+        <v>24954000</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C90" t="n">
+        <v>25256</v>
+      </c>
+      <c r="D90" t="n">
+        <v>12847.787</v>
+      </c>
+      <c r="E90" t="n">
+        <v>10091</v>
+      </c>
+      <c r="F90" t="n">
+        <v>74968916.5554</v>
+      </c>
+      <c r="G90" t="n">
+        <v>31861870.298</v>
+      </c>
+      <c r="H90" t="n">
+        <v>27861042</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C91" t="n">
+        <v>24300</v>
+      </c>
+      <c r="D91" t="n">
+        <v>12371</v>
+      </c>
+      <c r="E91" t="n">
+        <v>9442</v>
+      </c>
+      <c r="F91" t="n">
+        <v>77975735.4442</v>
+      </c>
+      <c r="G91" t="n">
+        <v>39335531.998</v>
+      </c>
+      <c r="H91" t="n">
+        <v>27893432</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C92" t="n">
+        <v>23428</v>
+      </c>
+      <c r="D92" t="n">
+        <v>11714</v>
+      </c>
+      <c r="E92" t="n">
+        <v>8967</v>
+      </c>
+      <c r="F92" t="n">
+        <v>71720004.5256</v>
+      </c>
+      <c r="G92" t="n">
+        <v>36587678.66</v>
+      </c>
+      <c r="H92" t="n">
+        <v>24696739</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C93" t="n">
+        <v>22424</v>
+      </c>
+      <c r="D93" t="n">
+        <v>11210.78</v>
+      </c>
+      <c r="E93" t="n">
+        <v>8105</v>
+      </c>
+      <c r="F93" t="n">
+        <v>82403423.3324</v>
+      </c>
+      <c r="G93" t="n">
+        <v>36065958.65</v>
+      </c>
+      <c r="H93" t="n">
+        <v>24820229</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C94" t="n">
+        <v>22524</v>
+      </c>
+      <c r="D94" t="n">
+        <v>11264.3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>7735</v>
+      </c>
+      <c r="F94" t="n">
+        <v>95955283.7588</v>
+      </c>
+      <c r="G94" t="n">
+        <v>37456630.596</v>
+      </c>
+      <c r="H94" t="n">
+        <v>26587640</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" t="n">
         <v>2024</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C95" t="n">
         <v>20108</v>
       </c>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35" t="n">
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95" t="n">
         <v>87586941.5088</v>
       </c>
-      <c r="G35"/>
-      <c r="H35"/>
+      <c r="G95"/>
+      <c r="H95"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2196,16 +4916,16 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
       <c r="I2" t="n">
-        <v>54078.656</v>
+        <v>4791.424</v>
       </c>
       <c r="J2"/>
     </row>
@@ -2220,16 +4940,16 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3" t="n">
-        <v>53983.636</v>
+        <v>4793.228</v>
       </c>
       <c r="J3"/>
     </row>
@@ -2244,16 +4964,16 @@
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" t="n">
-        <v>64109.577</v>
+        <v>4003.076</v>
       </c>
       <c r="J4"/>
     </row>
@@ -2268,16 +4988,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5" t="n">
-        <v>63962.275</v>
+        <v>4002.912</v>
       </c>
       <c r="J5"/>
     </row>
@@ -2292,16 +5012,16 @@
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="G6"/>
       <c r="H6"/>
       <c r="I6" t="n">
-        <v>327630.3</v>
+        <v>10020.439</v>
       </c>
       <c r="J6"/>
     </row>
@@ -2316,26 +5036,18 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
+        <v>2018</v>
+      </c>
+      <c r="E7"/>
       <c r="F7" t="n">
-        <v>85</v>
-      </c>
-      <c r="G7" t="n">
-        <v>85</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G7"/>
+      <c r="H7"/>
       <c r="I7" t="n">
-        <v>359672.544</v>
-      </c>
-      <c r="J7" t="n">
-        <v>359990</v>
-      </c>
+        <v>54078.656</v>
+      </c>
+      <c r="J7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -2348,17 +5060,17 @@
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8"/>
+        <v>2019</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8" t="n">
+        <v>27</v>
+      </c>
       <c r="G8"/>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8"/>
+      <c r="H8"/>
+      <c r="I8" t="n">
+        <v>53983.636</v>
+      </c>
       <c r="J8"/>
     </row>
     <row r="9">
@@ -2366,127 +5078,103 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>2018</v>
-      </c>
-      <c r="E9" t="n">
-        <v>11224.68</v>
-      </c>
+        <v>2020</v>
+      </c>
+      <c r="E9"/>
       <c r="F9" t="n">
-        <v>935.448</v>
-      </c>
-      <c r="G9" t="n">
-        <v>936</v>
-      </c>
-      <c r="H9" t="n">
-        <v>21307854.1656</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G9"/>
+      <c r="H9"/>
       <c r="I9" t="n">
-        <v>1779721.344</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1776000</v>
-      </c>
+        <v>64109.577</v>
+      </c>
+      <c r="J9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E10" t="n">
-        <v>12101.52</v>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="E10"/>
       <c r="F10" t="n">
-        <v>1007.476</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1008.46</v>
-      </c>
-      <c r="H10" t="n">
-        <v>23809591.872</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G10"/>
+      <c r="H10"/>
       <c r="I10" t="n">
-        <v>1983547.674</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1984132</v>
-      </c>
+        <v>63962.275</v>
+      </c>
+      <c r="J10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E11" t="n">
-        <v>6206.16</v>
-      </c>
+        <v>2022</v>
+      </c>
+      <c r="E11"/>
       <c r="F11" t="n">
-        <v>511.2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>517.18</v>
-      </c>
-      <c r="H11" t="n">
-        <v>9831096.886</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G11"/>
+      <c r="H11"/>
       <c r="I11" t="n">
-        <v>808215.136</v>
-      </c>
-      <c r="J11" t="n">
-        <v>819258</v>
-      </c>
+        <v>327630.3</v>
+      </c>
+      <c r="J11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E12" t="n">
-        <v>10921.2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>910.13</v>
+        <v>85</v>
       </c>
       <c r="G12" t="n">
-        <v>860.5</v>
+        <v>85</v>
       </c>
       <c r="H12" t="n">
-        <v>20058325.8792</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1671808.84</v>
+        <v>359672.544</v>
       </c>
       <c r="J12" t="n">
-        <v>1599854</v>
+        <v>359990</v>
       </c>
     </row>
     <row r="13">
@@ -2494,32 +5182,24 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E13" t="n">
-        <v>13147.68</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1095.63</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1095.64</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13"/>
       <c r="H13" t="n">
-        <v>30712050.3828</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2558545.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2559338</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I13"/>
+      <c r="J13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -2529,28 +5209,20 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E14" t="n">
-        <v>10314.14</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1016.948</v>
-      </c>
+        <v>2010</v>
+      </c>
+      <c r="E14"/>
+      <c r="F14"/>
       <c r="G14" t="n">
-        <v>1031.42</v>
-      </c>
-      <c r="H14" t="n">
-        <v>30983660.16</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3030209.952</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="H14"/>
+      <c r="I14"/>
       <c r="J14" t="n">
-        <v>3098370</v>
+        <v>2385000</v>
       </c>
     </row>
     <row r="15">
@@ -2564,16 +5236,14 @@
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E15" t="n">
-        <v>6616.3176</v>
-      </c>
-      <c r="F15"/>
+        <v>2006</v>
+      </c>
+      <c r="E15"/>
+      <c r="F15" t="n">
+        <v>3560</v>
+      </c>
       <c r="G15"/>
-      <c r="H15" t="n">
-        <v>17189192.5016</v>
-      </c>
+      <c r="H15"/>
       <c r="I15"/>
       <c r="J15"/>
     </row>
@@ -2585,29 +5255,19 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>2018</v>
-      </c>
-      <c r="E16" t="n">
-        <v>576397.2</v>
-      </c>
+        <v>2007</v>
+      </c>
+      <c r="E16"/>
       <c r="F16" t="n">
-        <v>48000</v>
-      </c>
-      <c r="G16" t="n">
-        <v>48033</v>
-      </c>
-      <c r="H16" t="n">
-        <v>783886096.8</v>
-      </c>
-      <c r="I16" t="n">
-        <v>63922516.448</v>
-      </c>
-      <c r="J16" t="n">
-        <v>65324000</v>
-      </c>
+        <v>3560</v>
+      </c>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -2617,29 +5277,21 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>2019</v>
+        <v>2008</v>
       </c>
       <c r="E17" t="n">
-        <v>479444.76</v>
+        <v>36006</v>
       </c>
       <c r="F17" t="n">
-        <v>40050</v>
-      </c>
-      <c r="G17" t="n">
-        <v>40738</v>
-      </c>
-      <c r="H17" t="n">
-        <v>617691522.36</v>
-      </c>
-      <c r="I17" t="n">
-        <v>61860862.226</v>
-      </c>
-      <c r="J17" t="n">
-        <v>52842106</v>
-      </c>
+        <v>3060</v>
+      </c>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -2649,29 +5301,23 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>2020</v>
+        <v>2009</v>
       </c>
       <c r="E18" t="n">
-        <v>411231.84</v>
+        <v>37080</v>
       </c>
       <c r="F18" t="n">
-        <v>34250</v>
-      </c>
-      <c r="G18" t="n">
-        <v>34870.6</v>
-      </c>
+        <v>2060</v>
+      </c>
+      <c r="G18"/>
       <c r="H18" t="n">
-        <v>632046420.3696</v>
-      </c>
-      <c r="I18" t="n">
-        <v>55519554.063</v>
-      </c>
-      <c r="J18" t="n">
-        <v>53981390</v>
-      </c>
+        <v>52144282.98</v>
+      </c>
+      <c r="I18"/>
+      <c r="J18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -2681,29 +5327,25 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>2021</v>
+        <v>2010</v>
       </c>
       <c r="E19" t="n">
-        <v>416415</v>
+        <v>37080</v>
       </c>
       <c r="F19" t="n">
-        <v>34700</v>
-      </c>
-      <c r="G19" t="n">
-        <v>34916.915</v>
-      </c>
+        <v>2060</v>
+      </c>
+      <c r="G19"/>
       <c r="H19" t="n">
-        <v>842983446.306</v>
+        <v>46958884.92</v>
       </c>
       <c r="I19" t="n">
-        <v>65916453.265</v>
-      </c>
-      <c r="J19" t="n">
-        <v>71468430</v>
-      </c>
+        <v>3146536.8</v>
+      </c>
+      <c r="J19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -2713,29 +5355,25 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="E20" t="n">
-        <v>382605.48</v>
+        <v>56700</v>
       </c>
       <c r="F20" t="n">
-        <v>31870</v>
-      </c>
-      <c r="G20" t="n">
-        <v>31883.79</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="G20"/>
       <c r="H20" t="n">
-        <v>694341304.68</v>
+        <v>84434273.64</v>
       </c>
       <c r="I20" t="n">
-        <v>61607799.25</v>
-      </c>
-      <c r="J20" t="n">
-        <v>57288459</v>
-      </c>
+        <v>594237.6</v>
+      </c>
+      <c r="J20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -2745,29 +5383,25 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="E21" t="n">
-        <v>409688.4</v>
+        <v>56700</v>
       </c>
       <c r="F21" t="n">
-        <v>34140.7</v>
-      </c>
-      <c r="G21" t="n">
-        <v>34140.7</v>
-      </c>
+        <v>450.546</v>
+      </c>
+      <c r="G21"/>
       <c r="H21" t="n">
-        <v>723029154.384</v>
+        <v>82787986.26</v>
       </c>
       <c r="I21" t="n">
-        <v>60087723.696</v>
-      </c>
-      <c r="J21" t="n">
-        <v>60252420</v>
-      </c>
+        <v>684691.062</v>
+      </c>
+      <c r="J21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -2777,629 +5411,2767 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="E22" t="n">
-        <v>306014.4</v>
-      </c>
-      <c r="F22"/>
-      <c r="G22"/>
+        <v>24000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2000</v>
+      </c>
       <c r="H22" t="n">
-        <v>535501741.0092</v>
-      </c>
-      <c r="I22"/>
-      <c r="J22"/>
+        <v>30715224.48</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3066864.944</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2559000</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="E23" t="n">
-        <v>11224.68</v>
+        <v>8952.04</v>
       </c>
       <c r="F23" t="n">
-        <v>935.448</v>
+        <v>746.045</v>
       </c>
       <c r="G23" t="n">
-        <v>936</v>
+        <v>746</v>
       </c>
       <c r="H23" t="n">
-        <v>21307854.1656</v>
+        <v>14336640.68</v>
       </c>
       <c r="I23" t="n">
-        <v>1779721.344</v>
+        <v>1432256.936</v>
       </c>
       <c r="J23" t="n">
-        <v>1776000</v>
+        <v>1195000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="E24" t="n">
-        <v>12101.52</v>
+        <v>9581.52</v>
       </c>
       <c r="F24" t="n">
-        <v>1007.476</v>
+        <v>798.477</v>
       </c>
       <c r="G24" t="n">
-        <v>1008.46</v>
+        <v>798</v>
       </c>
       <c r="H24" t="n">
-        <v>23809591.872</v>
+        <v>17321444.52</v>
       </c>
       <c r="I24" t="n">
-        <v>1983547.674</v>
+        <v>1444902.074</v>
       </c>
       <c r="J24" t="n">
-        <v>1984132</v>
+        <v>1443000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="E25" t="n">
-        <v>6206.16</v>
+        <v>9150.96</v>
       </c>
       <c r="F25" t="n">
-        <v>511.2</v>
+        <v>762.644</v>
       </c>
       <c r="G25" t="n">
-        <v>517.18</v>
+        <v>763</v>
       </c>
       <c r="H25" t="n">
-        <v>9831096.886</v>
+        <v>20146474.44</v>
       </c>
       <c r="I25" t="n">
-        <v>808215.136</v>
+        <v>1447702.664</v>
       </c>
       <c r="J25" t="n">
-        <v>819258</v>
+        <v>1679000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="E26" t="n">
-        <v>10921.2</v>
+        <v>11781.6</v>
       </c>
       <c r="F26" t="n">
-        <v>910.13</v>
+        <v>981.854</v>
       </c>
       <c r="G26" t="n">
-        <v>860.5</v>
+        <v>982</v>
       </c>
       <c r="H26" t="n">
-        <v>20058325.8792</v>
+        <v>21495389.88</v>
       </c>
       <c r="I26" t="n">
-        <v>1671808.84</v>
+        <v>1791869.502</v>
       </c>
       <c r="J26" t="n">
-        <v>1599854</v>
+        <v>1792000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="E27" t="n">
-        <v>13147.68</v>
+        <v>11224.68</v>
       </c>
       <c r="F27" t="n">
-        <v>1095.63</v>
+        <v>935.448</v>
       </c>
       <c r="G27" t="n">
-        <v>1095.64</v>
+        <v>936</v>
       </c>
       <c r="H27" t="n">
-        <v>30712050.3828</v>
+        <v>21307854.1656</v>
       </c>
       <c r="I27" t="n">
-        <v>2558545.7</v>
+        <v>1779721.344</v>
       </c>
       <c r="J27" t="n">
-        <v>2559338</v>
+        <v>1776000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="E28" t="n">
-        <v>10314.14</v>
+        <v>12101.52</v>
       </c>
       <c r="F28" t="n">
-        <v>1016.948</v>
+        <v>1007.476</v>
       </c>
       <c r="G28" t="n">
-        <v>1031.42</v>
+        <v>1008.46</v>
       </c>
       <c r="H28" t="n">
-        <v>30983660.16</v>
+        <v>23809591.872</v>
       </c>
       <c r="I28" t="n">
-        <v>3030209.952</v>
+        <v>1983547.674</v>
       </c>
       <c r="J28" t="n">
-        <v>3098370</v>
+        <v>1984132</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E29" t="n">
-        <v>6616.3176</v>
-      </c>
-      <c r="F29"/>
-      <c r="G29"/>
+        <v>6206.16</v>
+      </c>
+      <c r="F29" t="n">
+        <v>511.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>517.18</v>
+      </c>
       <c r="H29" t="n">
-        <v>17189192.5016</v>
-      </c>
-      <c r="I29"/>
-      <c r="J29"/>
+        <v>9831096.886</v>
+      </c>
+      <c r="I29" t="n">
+        <v>808215.136</v>
+      </c>
+      <c r="J29" t="n">
+        <v>819258</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="E30" t="n">
-        <v>576397.2</v>
+        <v>10921.2</v>
       </c>
       <c r="F30" t="n">
-        <v>48000</v>
+        <v>910.13</v>
       </c>
       <c r="G30" t="n">
-        <v>48033</v>
+        <v>860.5</v>
       </c>
       <c r="H30" t="n">
-        <v>783886096.8</v>
+        <v>20058325.8792</v>
       </c>
       <c r="I30" t="n">
-        <v>63922516.448</v>
+        <v>1671808.84</v>
       </c>
       <c r="J30" t="n">
-        <v>65324000</v>
+        <v>1599854</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="E31" t="n">
-        <v>479444.76</v>
+        <v>13147.68</v>
       </c>
       <c r="F31" t="n">
-        <v>40050</v>
+        <v>1095.63</v>
       </c>
       <c r="G31" t="n">
-        <v>40738</v>
+        <v>1095.64</v>
       </c>
       <c r="H31" t="n">
-        <v>617691522.36</v>
+        <v>30712050.3828</v>
       </c>
       <c r="I31" t="n">
-        <v>61860862.226</v>
+        <v>2558545.7</v>
       </c>
       <c r="J31" t="n">
-        <v>52842106</v>
+        <v>2559338</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="E32" t="n">
-        <v>411231.84</v>
+        <v>10314.14</v>
       </c>
       <c r="F32" t="n">
-        <v>34250</v>
+        <v>1016.948</v>
       </c>
       <c r="G32" t="n">
-        <v>34870.6</v>
+        <v>1031.42</v>
       </c>
       <c r="H32" t="n">
-        <v>632046420.3696</v>
+        <v>30983660.16</v>
       </c>
       <c r="I32" t="n">
-        <v>55519554.063</v>
+        <v>3030209.952</v>
       </c>
       <c r="J32" t="n">
-        <v>53981390</v>
+        <v>3098370</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="E33" t="n">
-        <v>416415</v>
-      </c>
-      <c r="F33" t="n">
-        <v>34700</v>
-      </c>
-      <c r="G33" t="n">
-        <v>34916.915</v>
-      </c>
+        <v>6616.3176</v>
+      </c>
+      <c r="F33"/>
+      <c r="G33"/>
       <c r="H33" t="n">
-        <v>842983446.306</v>
-      </c>
-      <c r="I33" t="n">
-        <v>65916453.265</v>
-      </c>
-      <c r="J33" t="n">
-        <v>71468430</v>
-      </c>
+        <v>17189192.5016</v>
+      </c>
+      <c r="I33"/>
+      <c r="J33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
         <v>11</v>
       </c>
       <c r="D34" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E34" t="n">
-        <v>382605.48</v>
-      </c>
+        <v>2006</v>
+      </c>
+      <c r="E34"/>
       <c r="F34" t="n">
-        <v>31870</v>
-      </c>
-      <c r="G34" t="n">
-        <v>31883.79</v>
-      </c>
-      <c r="H34" t="n">
-        <v>694341304.68</v>
-      </c>
-      <c r="I34" t="n">
-        <v>61607799.25</v>
-      </c>
-      <c r="J34" t="n">
-        <v>57288459</v>
-      </c>
+        <v>34653</v>
+      </c>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E35" t="n">
-        <v>409688.4</v>
-      </c>
+        <v>2007</v>
+      </c>
+      <c r="E35"/>
       <c r="F35" t="n">
-        <v>34140.7</v>
-      </c>
-      <c r="G35" t="n">
-        <v>34140.7</v>
-      </c>
-      <c r="H35" t="n">
-        <v>723029154.384</v>
-      </c>
-      <c r="I35" t="n">
-        <v>60087723.696</v>
-      </c>
-      <c r="J35" t="n">
-        <v>60252420</v>
-      </c>
+        <v>47121</v>
+      </c>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>2024</v>
+        <v>2008</v>
       </c>
       <c r="E36" t="n">
-        <v>306014.4</v>
-      </c>
-      <c r="F36"/>
+        <v>455476.8</v>
+      </c>
+      <c r="F36" t="n">
+        <v>38150.7</v>
+      </c>
       <c r="G36"/>
       <c r="H36" t="n">
-        <v>535501741.0092</v>
+        <v>808928799.24</v>
       </c>
       <c r="I36"/>
       <c r="J36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>2018</v>
-      </c>
-      <c r="E37"/>
+        <v>2009</v>
+      </c>
+      <c r="E37" t="n">
+        <v>857316.6</v>
+      </c>
       <c r="F37" t="n">
-        <v>27</v>
+        <v>47628.6</v>
       </c>
       <c r="G37"/>
-      <c r="H37"/>
-      <c r="I37" t="n">
-        <v>54078.656</v>
-      </c>
+      <c r="H37" t="n">
+        <v>1045246791.24</v>
+      </c>
+      <c r="I37"/>
       <c r="J37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>2019</v>
-      </c>
-      <c r="E38"/>
+        <v>2010</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1083333.6</v>
+      </c>
       <c r="F38" t="n">
-        <v>27</v>
-      </c>
-      <c r="G38"/>
-      <c r="H38"/>
+        <v>60185.1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>60185</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1321483124.88</v>
+      </c>
       <c r="I38" t="n">
-        <v>53983.636</v>
-      </c>
-      <c r="J38"/>
+        <v>87817013.416</v>
+      </c>
+      <c r="J38" t="n">
+        <v>73416000</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
       </c>
       <c r="D39" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E39"/>
+        <v>2011</v>
+      </c>
+      <c r="E39" t="n">
+        <v>708838.2</v>
+      </c>
       <c r="F39" t="n">
-        <v>32</v>
-      </c>
-      <c r="G39"/>
-      <c r="H39"/>
+        <v>39379.9</v>
+      </c>
+      <c r="G39" t="n">
+        <v>39380</v>
+      </c>
+      <c r="H39" t="n">
+        <v>944243010</v>
+      </c>
       <c r="I39" t="n">
-        <v>64109.577</v>
-      </c>
-      <c r="J39"/>
+        <v>65844807.556</v>
+      </c>
+      <c r="J39" t="n">
+        <v>52458000</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
       </c>
       <c r="D40" t="n">
-        <v>2021</v>
-      </c>
-      <c r="E40"/>
+        <v>2012</v>
+      </c>
+      <c r="E40" t="n">
+        <v>765709.2</v>
+      </c>
       <c r="F40" t="n">
-        <v>32</v>
-      </c>
-      <c r="G40"/>
-      <c r="H40"/>
+        <v>42539.4</v>
+      </c>
+      <c r="G40" t="n">
+        <v>42539</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1301235120</v>
+      </c>
       <c r="I40" t="n">
-        <v>63962.275</v>
-      </c>
-      <c r="J40"/>
+        <v>83755921.678</v>
+      </c>
+      <c r="J40" t="n">
+        <v>72291000</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
       </c>
       <c r="D41" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E41"/>
+        <v>2013</v>
+      </c>
+      <c r="E41" t="n">
+        <v>480844.32</v>
+      </c>
       <c r="F41" t="n">
-        <v>77</v>
-      </c>
-      <c r="G41"/>
-      <c r="H41"/>
+        <v>40070</v>
+      </c>
+      <c r="G41" t="n">
+        <v>40070</v>
+      </c>
+      <c r="H41" t="n">
+        <v>918637398</v>
+      </c>
       <c r="I41" t="n">
-        <v>327630.3</v>
-      </c>
-      <c r="J41"/>
+        <v>91725658.134</v>
+      </c>
+      <c r="J41" t="n">
+        <v>76553000</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>688368.24</v>
       </c>
       <c r="F42" t="n">
-        <v>85</v>
+        <v>57364</v>
       </c>
       <c r="G42" t="n">
-        <v>85</v>
+        <v>57364</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>885666753.12</v>
       </c>
       <c r="I42" t="n">
-        <v>359672.544</v>
+        <v>88444708</v>
       </c>
       <c r="J42" t="n">
-        <v>359990</v>
+        <v>73805000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E43" t="n">
+        <v>682971.48</v>
+      </c>
+      <c r="F43" t="n">
+        <v>56800</v>
+      </c>
+      <c r="G43" t="n">
+        <v>56915</v>
+      </c>
+      <c r="H43" t="n">
+        <v>845360242.48</v>
+      </c>
+      <c r="I43" t="n">
+        <v>77490443.866</v>
+      </c>
+      <c r="J43" t="n">
+        <v>70447000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E44" t="n">
+        <v>677681.28</v>
+      </c>
+      <c r="F44" t="n">
+        <v>56300</v>
+      </c>
+      <c r="G44" t="n">
+        <v>56474</v>
+      </c>
+      <c r="H44" t="n">
+        <v>723406552.36</v>
+      </c>
+      <c r="I44" t="n">
+        <v>58042148.064</v>
+      </c>
+      <c r="J44" t="n">
+        <v>60284000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E45" t="n">
+        <v>554514</v>
+      </c>
+      <c r="F45" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G45" t="n">
+        <v>46209</v>
+      </c>
+      <c r="H45" t="n">
+        <v>768769982.136</v>
+      </c>
+      <c r="I45" t="n">
+        <v>62320079.817</v>
+      </c>
+      <c r="J45" t="n">
+        <v>64064000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E46" t="n">
+        <v>576397.2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>48000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>48033</v>
+      </c>
+      <c r="H46" t="n">
+        <v>783886096.8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>63922516.448</v>
+      </c>
+      <c r="J46" t="n">
+        <v>65324000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E47" t="n">
+        <v>479444.76</v>
+      </c>
+      <c r="F47" t="n">
+        <v>40050</v>
+      </c>
+      <c r="G47" t="n">
+        <v>40738</v>
+      </c>
+      <c r="H47" t="n">
+        <v>617691522.36</v>
+      </c>
+      <c r="I47" t="n">
+        <v>61860862.226</v>
+      </c>
+      <c r="J47" t="n">
+        <v>52842106</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E48" t="n">
+        <v>411231.84</v>
+      </c>
+      <c r="F48" t="n">
+        <v>34250</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34870.6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>632046420.3696</v>
+      </c>
+      <c r="I48" t="n">
+        <v>55519554.063</v>
+      </c>
+      <c r="J48" t="n">
+        <v>53981390</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E49" t="n">
+        <v>416415</v>
+      </c>
+      <c r="F49" t="n">
+        <v>34700</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34916.915</v>
+      </c>
+      <c r="H49" t="n">
+        <v>842983446.306</v>
+      </c>
+      <c r="I49" t="n">
+        <v>65916453.265</v>
+      </c>
+      <c r="J49" t="n">
+        <v>71468430</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E50" t="n">
+        <v>382605.48</v>
+      </c>
+      <c r="F50" t="n">
+        <v>31870</v>
+      </c>
+      <c r="G50" t="n">
+        <v>31883.79</v>
+      </c>
+      <c r="H50" t="n">
+        <v>694341304.68</v>
+      </c>
+      <c r="I50" t="n">
+        <v>61607799.25</v>
+      </c>
+      <c r="J50" t="n">
+        <v>57288459</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E51" t="n">
+        <v>409688.4</v>
+      </c>
+      <c r="F51" t="n">
+        <v>34140.7</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34140.7</v>
+      </c>
+      <c r="H51" t="n">
+        <v>723029154.384</v>
+      </c>
+      <c r="I51" t="n">
+        <v>60087723.696</v>
+      </c>
+      <c r="J51" t="n">
+        <v>60252420</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E52" t="n">
+        <v>306014.4</v>
+      </c>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52" t="n">
+        <v>535501741.0092</v>
+      </c>
+      <c r="I52"/>
+      <c r="J52"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E53" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>31426.02</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2190.056</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E54" t="n">
+        <v>165.24</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9</v>
+      </c>
+      <c r="H54" t="n">
+        <v>201167.46</v>
+      </c>
+      <c r="I54" t="n">
+        <v>12859.814</v>
+      </c>
+      <c r="J54" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E55" t="n">
+        <v>196.68</v>
+      </c>
+      <c r="F55" t="n">
+        <v>16</v>
+      </c>
+      <c r="G55" t="n">
+        <v>16</v>
+      </c>
+      <c r="H55" t="n">
+        <v>315872.4</v>
+      </c>
+      <c r="I55" t="n">
+        <v>28195.618</v>
+      </c>
+      <c r="J55" t="n">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E56" t="n">
+        <v>252</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21</v>
+      </c>
+      <c r="G56" t="n">
+        <v>21</v>
+      </c>
+      <c r="H56" t="n">
+        <v>313338.84</v>
+      </c>
+      <c r="I56" t="n">
+        <v>31141.55</v>
+      </c>
+      <c r="J56" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E57" t="n">
+        <v>417.84</v>
+      </c>
+      <c r="F57" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="G57" t="n">
+        <v>35</v>
+      </c>
+      <c r="H57" t="n">
+        <v>607420.68</v>
+      </c>
+      <c r="I57" t="n">
+        <v>50730.284</v>
+      </c>
+      <c r="J57" t="n">
+        <v>51000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E58" t="n">
+        <v>295.68</v>
+      </c>
+      <c r="F58" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="G58" t="n">
+        <v>25</v>
+      </c>
+      <c r="H58" t="n">
+        <v>427347.93</v>
+      </c>
+      <c r="I58" t="n">
+        <v>35394.312</v>
+      </c>
+      <c r="J58" t="n">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
         <v>18</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59" t="n">
+        <v>300</v>
+      </c>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59" t="n">
+        <v>2385000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E60"/>
+      <c r="F60" t="n">
+        <v>3560</v>
+      </c>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E61"/>
+      <c r="F61" t="n">
+        <v>3560</v>
+      </c>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E62" t="n">
+        <v>36006</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3060</v>
+      </c>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E63" t="n">
+        <v>37080</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2060</v>
+      </c>
+      <c r="G63"/>
+      <c r="H63" t="n">
+        <v>52144282.98</v>
+      </c>
+      <c r="I63"/>
+      <c r="J63"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E64" t="n">
+        <v>37080</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2060</v>
+      </c>
+      <c r="G64"/>
+      <c r="H64" t="n">
+        <v>46958884.92</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3146536.8</v>
+      </c>
+      <c r="J64"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E65" t="n">
+        <v>56700</v>
+      </c>
+      <c r="F65" t="n">
+        <v>420</v>
+      </c>
+      <c r="G65"/>
+      <c r="H65" t="n">
+        <v>84434273.64</v>
+      </c>
+      <c r="I65" t="n">
+        <v>594237.6</v>
+      </c>
+      <c r="J65"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E66" t="n">
+        <v>56700</v>
+      </c>
+      <c r="F66" t="n">
+        <v>450.546</v>
+      </c>
+      <c r="G66"/>
+      <c r="H66" t="n">
+        <v>82787986.26</v>
+      </c>
+      <c r="I66" t="n">
+        <v>684691.062</v>
+      </c>
+      <c r="J66"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>18</v>
+      </c>
+      <c r="B67" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E67" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H67" t="n">
+        <v>30715224.48</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3066864.944</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2559000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E68" t="n">
+        <v>8952.04</v>
+      </c>
+      <c r="F68" t="n">
+        <v>746.045</v>
+      </c>
+      <c r="G68" t="n">
+        <v>746</v>
+      </c>
+      <c r="H68" t="n">
+        <v>14336640.68</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1432256.936</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1195000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E69" t="n">
+        <v>9581.52</v>
+      </c>
+      <c r="F69" t="n">
+        <v>798.477</v>
+      </c>
+      <c r="G69" t="n">
+        <v>798</v>
+      </c>
+      <c r="H69" t="n">
+        <v>17321444.52</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1444902.074</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1443000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E70" t="n">
+        <v>9150.96</v>
+      </c>
+      <c r="F70" t="n">
+        <v>762.644</v>
+      </c>
+      <c r="G70" t="n">
+        <v>763</v>
+      </c>
+      <c r="H70" t="n">
+        <v>20146474.44</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1447702.664</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1679000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E71" t="n">
+        <v>11781.6</v>
+      </c>
+      <c r="F71" t="n">
+        <v>981.854</v>
+      </c>
+      <c r="G71" t="n">
+        <v>982</v>
+      </c>
+      <c r="H71" t="n">
+        <v>21495389.88</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1791869.502</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1792000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E72" t="n">
+        <v>11224.68</v>
+      </c>
+      <c r="F72" t="n">
+        <v>935.448</v>
+      </c>
+      <c r="G72" t="n">
+        <v>936</v>
+      </c>
+      <c r="H72" t="n">
+        <v>21307854.1656</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1779721.344</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1776000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>18</v>
+      </c>
+      <c r="B73" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E73" t="n">
+        <v>12101.52</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1007.476</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1008.46</v>
+      </c>
+      <c r="H73" t="n">
+        <v>23809591.872</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1983547.674</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1984132</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E74" t="n">
+        <v>6206.16</v>
+      </c>
+      <c r="F74" t="n">
+        <v>511.2</v>
+      </c>
+      <c r="G74" t="n">
+        <v>517.18</v>
+      </c>
+      <c r="H74" t="n">
+        <v>9831096.886</v>
+      </c>
+      <c r="I74" t="n">
+        <v>808215.136</v>
+      </c>
+      <c r="J74" t="n">
+        <v>819258</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>18</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10921.2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>910.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>860.5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>20058325.8792</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1671808.84</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1599854</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>18</v>
+      </c>
+      <c r="B76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E76" t="n">
+        <v>13147.68</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1095.63</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1095.64</v>
+      </c>
+      <c r="H76" t="n">
+        <v>30712050.3828</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2558545.7</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2559338</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>18</v>
+      </c>
+      <c r="B77" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E77" t="n">
+        <v>10314.14</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1016.948</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1031.42</v>
+      </c>
+      <c r="H77" t="n">
+        <v>30983660.16</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3030209.952</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3098370</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>18</v>
+      </c>
+      <c r="B78" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E78" t="n">
+        <v>6616.3176</v>
+      </c>
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="H78" t="n">
+        <v>17189192.5016</v>
+      </c>
+      <c r="I78"/>
+      <c r="J78"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>18</v>
+      </c>
+      <c r="B79" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E79"/>
+      <c r="F79" t="n">
+        <v>34653</v>
+      </c>
+      <c r="G79"/>
+      <c r="H79"/>
+      <c r="I79"/>
+      <c r="J79"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>18</v>
+      </c>
+      <c r="B80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E80"/>
+      <c r="F80" t="n">
+        <v>47121</v>
+      </c>
+      <c r="G80"/>
+      <c r="H80"/>
+      <c r="I80"/>
+      <c r="J80"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>18</v>
+      </c>
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E81" t="n">
+        <v>455476.8</v>
+      </c>
+      <c r="F81" t="n">
+        <v>38150.7</v>
+      </c>
+      <c r="G81"/>
+      <c r="H81" t="n">
+        <v>808928799.24</v>
+      </c>
+      <c r="I81"/>
+      <c r="J81"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>18</v>
+      </c>
+      <c r="B82" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E82" t="n">
+        <v>857316.6</v>
+      </c>
+      <c r="F82" t="n">
+        <v>47628.6</v>
+      </c>
+      <c r="G82"/>
+      <c r="H82" t="n">
+        <v>1045246791.24</v>
+      </c>
+      <c r="I82"/>
+      <c r="J82"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>18</v>
+      </c>
+      <c r="B83" t="s">
+        <v>19</v>
+      </c>
+      <c r="C83" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1083333.6</v>
+      </c>
+      <c r="F83" t="n">
+        <v>60185.1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>60185</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1321483124.88</v>
+      </c>
+      <c r="I83" t="n">
+        <v>87817013.416</v>
+      </c>
+      <c r="J83" t="n">
+        <v>73416000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E84" t="n">
+        <v>708838.2</v>
+      </c>
+      <c r="F84" t="n">
+        <v>39379.9</v>
+      </c>
+      <c r="G84" t="n">
+        <v>39380</v>
+      </c>
+      <c r="H84" t="n">
+        <v>944243010</v>
+      </c>
+      <c r="I84" t="n">
+        <v>65844807.556</v>
+      </c>
+      <c r="J84" t="n">
+        <v>52458000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>18</v>
+      </c>
+      <c r="B85" t="s">
+        <v>19</v>
+      </c>
+      <c r="C85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E85" t="n">
+        <v>765709.2</v>
+      </c>
+      <c r="F85" t="n">
+        <v>42539.4</v>
+      </c>
+      <c r="G85" t="n">
+        <v>42539</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1301235120</v>
+      </c>
+      <c r="I85" t="n">
+        <v>83755921.678</v>
+      </c>
+      <c r="J85" t="n">
+        <v>72291000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>18</v>
+      </c>
+      <c r="B86" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E86" t="n">
+        <v>480844.32</v>
+      </c>
+      <c r="F86" t="n">
+        <v>40070</v>
+      </c>
+      <c r="G86" t="n">
+        <v>40070</v>
+      </c>
+      <c r="H86" t="n">
+        <v>918637398</v>
+      </c>
+      <c r="I86" t="n">
+        <v>91725658.134</v>
+      </c>
+      <c r="J86" t="n">
+        <v>76553000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>18</v>
+      </c>
+      <c r="B87" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E87" t="n">
+        <v>688368.24</v>
+      </c>
+      <c r="F87" t="n">
+        <v>57364</v>
+      </c>
+      <c r="G87" t="n">
+        <v>57364</v>
+      </c>
+      <c r="H87" t="n">
+        <v>885666753.12</v>
+      </c>
+      <c r="I87" t="n">
+        <v>88444708</v>
+      </c>
+      <c r="J87" t="n">
+        <v>73805000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E88" t="n">
+        <v>682971.48</v>
+      </c>
+      <c r="F88" t="n">
+        <v>56800</v>
+      </c>
+      <c r="G88" t="n">
+        <v>56915</v>
+      </c>
+      <c r="H88" t="n">
+        <v>845360242.48</v>
+      </c>
+      <c r="I88" t="n">
+        <v>77490443.866</v>
+      </c>
+      <c r="J88" t="n">
+        <v>70447000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>18</v>
+      </c>
+      <c r="B89" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E89" t="n">
+        <v>677681.28</v>
+      </c>
+      <c r="F89" t="n">
+        <v>56300</v>
+      </c>
+      <c r="G89" t="n">
+        <v>56474</v>
+      </c>
+      <c r="H89" t="n">
+        <v>723406552.36</v>
+      </c>
+      <c r="I89" t="n">
+        <v>58042148.064</v>
+      </c>
+      <c r="J89" t="n">
+        <v>60284000</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>18</v>
+      </c>
+      <c r="B90" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E90" t="n">
+        <v>554514</v>
+      </c>
+      <c r="F90" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G90" t="n">
+        <v>46209</v>
+      </c>
+      <c r="H90" t="n">
+        <v>768769982.136</v>
+      </c>
+      <c r="I90" t="n">
+        <v>62320079.817</v>
+      </c>
+      <c r="J90" t="n">
+        <v>64064000</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>18</v>
+      </c>
+      <c r="B91" t="s">
+        <v>19</v>
+      </c>
+      <c r="C91" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E91" t="n">
+        <v>576397.2</v>
+      </c>
+      <c r="F91" t="n">
+        <v>48000</v>
+      </c>
+      <c r="G91" t="n">
+        <v>48033</v>
+      </c>
+      <c r="H91" t="n">
+        <v>783886096.8</v>
+      </c>
+      <c r="I91" t="n">
+        <v>63922516.448</v>
+      </c>
+      <c r="J91" t="n">
+        <v>65324000</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>18</v>
+      </c>
+      <c r="B92" t="s">
+        <v>19</v>
+      </c>
+      <c r="C92" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E92" t="n">
+        <v>479444.76</v>
+      </c>
+      <c r="F92" t="n">
+        <v>40050</v>
+      </c>
+      <c r="G92" t="n">
+        <v>40738</v>
+      </c>
+      <c r="H92" t="n">
+        <v>617691522.36</v>
+      </c>
+      <c r="I92" t="n">
+        <v>61860862.226</v>
+      </c>
+      <c r="J92" t="n">
+        <v>52842106</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>18</v>
+      </c>
+      <c r="B93" t="s">
+        <v>19</v>
+      </c>
+      <c r="C93" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E93" t="n">
+        <v>411231.84</v>
+      </c>
+      <c r="F93" t="n">
+        <v>34250</v>
+      </c>
+      <c r="G93" t="n">
+        <v>34870.6</v>
+      </c>
+      <c r="H93" t="n">
+        <v>632046420.3696</v>
+      </c>
+      <c r="I93" t="n">
+        <v>55519554.063</v>
+      </c>
+      <c r="J93" t="n">
+        <v>53981390</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>18</v>
+      </c>
+      <c r="B94" t="s">
+        <v>19</v>
+      </c>
+      <c r="C94" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E94" t="n">
+        <v>416415</v>
+      </c>
+      <c r="F94" t="n">
+        <v>34700</v>
+      </c>
+      <c r="G94" t="n">
+        <v>34916.915</v>
+      </c>
+      <c r="H94" t="n">
+        <v>842983446.306</v>
+      </c>
+      <c r="I94" t="n">
+        <v>65916453.265</v>
+      </c>
+      <c r="J94" t="n">
+        <v>71468430</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>18</v>
+      </c>
+      <c r="B95" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E95" t="n">
+        <v>382605.48</v>
+      </c>
+      <c r="F95" t="n">
+        <v>31870</v>
+      </c>
+      <c r="G95" t="n">
+        <v>31883.79</v>
+      </c>
+      <c r="H95" t="n">
+        <v>694341304.68</v>
+      </c>
+      <c r="I95" t="n">
+        <v>61607799.25</v>
+      </c>
+      <c r="J95" t="n">
+        <v>57288459</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>18</v>
+      </c>
+      <c r="B96" t="s">
+        <v>19</v>
+      </c>
+      <c r="C96" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E96" t="n">
+        <v>409688.4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>34140.7</v>
+      </c>
+      <c r="G96" t="n">
+        <v>34140.7</v>
+      </c>
+      <c r="H96" t="n">
+        <v>723029154.384</v>
+      </c>
+      <c r="I96" t="n">
+        <v>60087723.696</v>
+      </c>
+      <c r="J96" t="n">
+        <v>60252420</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>18</v>
+      </c>
+      <c r="B97" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E97" t="n">
+        <v>306014.4</v>
+      </c>
+      <c r="F97"/>
+      <c r="G97"/>
+      <c r="H97" t="n">
+        <v>535501741.0092</v>
+      </c>
+      <c r="I97"/>
+      <c r="J97"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>18</v>
+      </c>
+      <c r="B98" t="s">
+        <v>19</v>
+      </c>
+      <c r="C98" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E98" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>31426.02</v>
+      </c>
+      <c r="I98" t="n">
+        <v>2190.056</v>
+      </c>
+      <c r="J98" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>18</v>
+      </c>
+      <c r="B99" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E99" t="n">
+        <v>165.24</v>
+      </c>
+      <c r="F99" t="n">
+        <v>9</v>
+      </c>
+      <c r="G99" t="n">
+        <v>9</v>
+      </c>
+      <c r="H99" t="n">
+        <v>201167.46</v>
+      </c>
+      <c r="I99" t="n">
+        <v>12859.814</v>
+      </c>
+      <c r="J99" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>18</v>
+      </c>
+      <c r="B100" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E100" t="n">
+        <v>196.68</v>
+      </c>
+      <c r="F100" t="n">
+        <v>16</v>
+      </c>
+      <c r="G100" t="n">
+        <v>16</v>
+      </c>
+      <c r="H100" t="n">
+        <v>315872.4</v>
+      </c>
+      <c r="I100" t="n">
+        <v>28195.618</v>
+      </c>
+      <c r="J100" t="n">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>18</v>
+      </c>
+      <c r="B101" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E101" t="n">
+        <v>252</v>
+      </c>
+      <c r="F101" t="n">
+        <v>21</v>
+      </c>
+      <c r="G101" t="n">
+        <v>21</v>
+      </c>
+      <c r="H101" t="n">
+        <v>313338.84</v>
+      </c>
+      <c r="I101" t="n">
+        <v>31141.55</v>
+      </c>
+      <c r="J101" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>18</v>
+      </c>
+      <c r="B102" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E102" t="n">
+        <v>417.84</v>
+      </c>
+      <c r="F102" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="G102" t="n">
+        <v>35</v>
+      </c>
+      <c r="H102" t="n">
+        <v>607420.68</v>
+      </c>
+      <c r="I102" t="n">
+        <v>50730.284</v>
+      </c>
+      <c r="J102" t="n">
+        <v>51000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>18</v>
+      </c>
+      <c r="B103" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E103" t="n">
+        <v>295.68</v>
+      </c>
+      <c r="F103" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="G103" t="n">
+        <v>25</v>
+      </c>
+      <c r="H103" t="n">
+        <v>427347.93</v>
+      </c>
+      <c r="I103" t="n">
+        <v>35394.312</v>
+      </c>
+      <c r="J103" t="n">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>18</v>
+      </c>
+      <c r="B104" t="s">
         <v>20</v>
       </c>
-      <c r="C43" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" t="n">
+      <c r="C104" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E104"/>
+      <c r="F104" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104" t="n">
+        <v>4791.424</v>
+      </c>
+      <c r="J104"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>18</v>
+      </c>
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E105"/>
+      <c r="F105" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="I105" t="n">
+        <v>4793.228</v>
+      </c>
+      <c r="J105"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>18</v>
+      </c>
+      <c r="B106" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E106"/>
+      <c r="F106" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="I106" t="n">
+        <v>4003.076</v>
+      </c>
+      <c r="J106"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>18</v>
+      </c>
+      <c r="B107" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E107"/>
+      <c r="F107" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107" t="n">
+        <v>4002.912</v>
+      </c>
+      <c r="J107"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>18</v>
+      </c>
+      <c r="B108" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E108"/>
+      <c r="F108" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108" t="n">
+        <v>10020.439</v>
+      </c>
+      <c r="J108"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>18</v>
+      </c>
+      <c r="B109" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E109"/>
+      <c r="F109" t="n">
+        <v>27</v>
+      </c>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="I109" t="n">
+        <v>54078.656</v>
+      </c>
+      <c r="J109"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>18</v>
+      </c>
+      <c r="B110" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E110"/>
+      <c r="F110" t="n">
+        <v>27</v>
+      </c>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110" t="n">
+        <v>53983.636</v>
+      </c>
+      <c r="J110"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>18</v>
+      </c>
+      <c r="B111" t="s">
+        <v>20</v>
+      </c>
+      <c r="C111" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E111"/>
+      <c r="F111" t="n">
+        <v>32</v>
+      </c>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="I111" t="n">
+        <v>64109.577</v>
+      </c>
+      <c r="J111"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>18</v>
+      </c>
+      <c r="B112" t="s">
+        <v>20</v>
+      </c>
+      <c r="C112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E112"/>
+      <c r="F112" t="n">
+        <v>32</v>
+      </c>
+      <c r="G112"/>
+      <c r="H112"/>
+      <c r="I112" t="n">
+        <v>63962.275</v>
+      </c>
+      <c r="J112"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>18</v>
+      </c>
+      <c r="B113" t="s">
+        <v>20</v>
+      </c>
+      <c r="C113" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E113"/>
+      <c r="F113" t="n">
+        <v>77</v>
+      </c>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="I113" t="n">
+        <v>327630.3</v>
+      </c>
+      <c r="J113"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>18</v>
+      </c>
+      <c r="B114" t="s">
+        <v>20</v>
+      </c>
+      <c r="C114" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>85</v>
+      </c>
+      <c r="G114" t="n">
+        <v>85</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>359672.544</v>
+      </c>
+      <c r="J114" t="n">
+        <v>359990</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>18</v>
+      </c>
+      <c r="B115" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" t="n">
         <v>2024</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E115" t="n">
         <v>0</v>
       </c>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43" t="n">
+      <c r="F115"/>
+      <c r="G115"/>
+      <c r="H115" t="n">
         <v>0</v>
       </c>
-      <c r="I43"/>
-      <c r="J43"/>
+      <c r="I115"/>
+      <c r="J115"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
